--- a/SIMULATION/EXPERIMENT MODEL/START/rekomendasi_paket.xlsx
+++ b/SIMULATION/EXPERIMENT MODEL/START/rekomendasi_paket.xlsx
@@ -547,14 +547,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungle Adventure</t>
+          <t>Kusuma Waterpark</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>55000</v>
+        <v>25000</v>
       </c>
       <c r="H2" t="n">
-        <v>55000</v>
+        <v>25000</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         <v>114000</v>
       </c>
       <c r="L2" t="n">
-        <v>5.57</v>
+        <v>5.64</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>12536</v>
+        <v>12689</v>
       </c>
       <c r="O2" t="n">
-        <v>364020</v>
+        <v>334173</v>
       </c>
       <c r="P2" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q2" t="n">
-        <v>4635980</v>
+        <v>665827</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -607,25 +607,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kahan Homestay</t>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>176740</v>
+        <v>182484</v>
       </c>
       <c r="E3" t="n">
-        <v>176740</v>
+        <v>182484</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungle Adventure</t>
+          <t>Kusuma Edukasi Pertanian</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>55000</v>
+        <v>25000</v>
       </c>
       <c r="H3" t="n">
-        <v>55000</v>
+        <v>25000</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         <v>114000</v>
       </c>
       <c r="L3" t="n">
-        <v>5.58</v>
+        <v>5.96</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -647,16 +647,16 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>12550</v>
+        <v>13406</v>
       </c>
       <c r="O3" t="n">
-        <v>358290</v>
+        <v>334890</v>
       </c>
       <c r="P3" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q3" t="n">
-        <v>4641710</v>
+        <v>665110</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -678,25 +678,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Super OYO 604 Cemara's Homestay</t>
+          <t>Kahan Homestay</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>182496</v>
+        <v>176740</v>
       </c>
       <c r="E4" t="n">
-        <v>182496</v>
+        <v>176740</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jungle Adventure</t>
+          <t>Kusuma Waterpark</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>55000</v>
+        <v>25000</v>
       </c>
       <c r="H4" t="n">
-        <v>55000</v>
+        <v>25000</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>114000</v>
       </c>
       <c r="L4" t="n">
-        <v>5.85</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -718,16 +718,16 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>13152</v>
+        <v>18497</v>
       </c>
       <c r="O4" t="n">
-        <v>364648</v>
+        <v>334237</v>
       </c>
       <c r="P4" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q4" t="n">
-        <v>4635352</v>
+        <v>665763</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -749,29 +749,29 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Omah Kalimosodo RedPartner near Stasiun Malang Kota Baru</t>
+          <t>Super OYO 604 Cemara's Homestay</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>176809</v>
+        <v>182496</v>
       </c>
       <c r="E5" t="n">
-        <v>176809</v>
+        <v>182496</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Taman Bentoel Trunojoyo Selatan</t>
+          <t>Kusuma Waterpark</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>55000</v>
+        <v>25000</v>
       </c>
       <c r="H5" t="n">
-        <v>55000</v>
+        <v>25000</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Warung Nasi Soto Gule Rawon Sawahan</t>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -781,7 +781,7 @@
         <v>114000</v>
       </c>
       <c r="L5" t="n">
-        <v>7.06</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -789,16 +789,16 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>15885</v>
+        <v>19068</v>
       </c>
       <c r="O5" t="n">
-        <v>361694</v>
+        <v>340564</v>
       </c>
       <c r="P5" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>4638306</v>
+        <v>659436</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -820,29 +820,29 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Junggo Tentrem</t>
+          <t>Kahan Homestay</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>176216</v>
+        <v>176740</v>
       </c>
       <c r="E6" t="n">
-        <v>176216</v>
+        <v>176740</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Taman Bentoel Trunojoyo Selatan</t>
+          <t>Kusuma Edukasi Pertanian</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>55000</v>
+        <v>25000</v>
       </c>
       <c r="H6" t="n">
-        <v>55000</v>
+        <v>25000</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Warung Nasi Soto Gule Rawon Sawahan</t>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -852,7 +852,7 @@
         <v>114000</v>
       </c>
       <c r="L6" t="n">
-        <v>8.06</v>
+        <v>8.57</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -860,16 +860,16 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>18142</v>
+        <v>19287</v>
       </c>
       <c r="O6" t="n">
-        <v>363358</v>
+        <v>335027</v>
       </c>
       <c r="P6" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q6" t="n">
-        <v>4636642</v>
+        <v>664973</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -891,39 +891,39 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The Grand Palace Hotel Malang</t>
+          <t>D'Fresh Guest House and Resto</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>318189</v>
+        <v>327600</v>
       </c>
       <c r="E7" t="n">
-        <v>318189</v>
+        <v>327600</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Masjid Agung Jami' Kota Malang</t>
+          <t>Hawai Waterpark</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>150000</v>
+        <v>85000</v>
       </c>
       <c r="H7" t="n">
-        <v>150000</v>
+        <v>85000</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Pondok Desa</t>
+          <t>Depot Shanghai</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>35000</v>
+        <v>34000</v>
       </c>
       <c r="K7" t="n">
-        <v>210000</v>
+        <v>204000</v>
       </c>
       <c r="L7" t="n">
-        <v>2.94</v>
+        <v>8.42</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6609</v>
+        <v>18939</v>
       </c>
       <c r="O7" t="n">
-        <v>684798</v>
+        <v>635539</v>
       </c>
       <c r="P7" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q7" t="n">
-        <v>4315202</v>
+        <v>364461</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -962,39 +962,39 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Semeru Hostel Malang</t>
+          <t>Hotel Grage Malang</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>307162</v>
+        <v>315315</v>
       </c>
       <c r="E8" t="n">
-        <v>307162</v>
+        <v>315315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Masjid Agung Jami' Kota Malang</t>
+          <t>Hawai Waterpark</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>150000</v>
+        <v>85000</v>
       </c>
       <c r="H8" t="n">
-        <v>150000</v>
+        <v>85000</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Pondok Desa</t>
+          <t>Depot Shanghai</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>35000</v>
+        <v>34000</v>
       </c>
       <c r="K8" t="n">
-        <v>210000</v>
+        <v>204000</v>
       </c>
       <c r="L8" t="n">
-        <v>3.29</v>
+        <v>10.49</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>7407</v>
+        <v>23598</v>
       </c>
       <c r="O8" t="n">
-        <v>674569</v>
+        <v>627913</v>
       </c>
       <c r="P8" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q8" t="n">
-        <v>4325431</v>
+        <v>372087</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1033,39 +1033,39 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The Grand Palace Hotel Malang</t>
+          <t>D'Fresh Guest House and Resto</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>318189</v>
+        <v>327600</v>
       </c>
       <c r="E9" t="n">
-        <v>318189</v>
+        <v>327600</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sweetmemoriesselfie</t>
+          <t>Hawai Waterpark</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>170000</v>
+        <v>85000</v>
       </c>
       <c r="H9" t="n">
-        <v>170000</v>
+        <v>85000</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Pondok Desa</t>
+          <t>Hot Cui Mie</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>35000</v>
+        <v>32250</v>
       </c>
       <c r="K9" t="n">
-        <v>210000</v>
+        <v>193500</v>
       </c>
       <c r="L9" t="n">
-        <v>3.39</v>
+        <v>10.91</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>7639</v>
+        <v>24546</v>
       </c>
       <c r="O9" t="n">
-        <v>705828</v>
+        <v>630646</v>
       </c>
       <c r="P9" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q9" t="n">
-        <v>4294172</v>
+        <v>369354</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1104,39 +1104,39 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Semeru Hostel Malang</t>
+          <t>Hotel Grage Malang</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>307162</v>
+        <v>315315</v>
       </c>
       <c r="E10" t="n">
-        <v>307162</v>
+        <v>315315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sweetmemoriesselfie</t>
+          <t>Hawai Waterpark</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>170000</v>
+        <v>85000</v>
       </c>
       <c r="H10" t="n">
-        <v>170000</v>
+        <v>85000</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Pondok Desa</t>
+          <t>Hot Cui Mie</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>35000</v>
+        <v>32250</v>
       </c>
       <c r="K10" t="n">
-        <v>210000</v>
+        <v>193500</v>
       </c>
       <c r="L10" t="n">
-        <v>4.07</v>
+        <v>13.51</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1144,16 +1144,16 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>9161</v>
+        <v>30396</v>
       </c>
       <c r="O10" t="n">
-        <v>696323</v>
+        <v>624211</v>
       </c>
       <c r="P10" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q10" t="n">
-        <v>4303677</v>
+        <v>375789</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1175,39 +1175,39 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RedDoorz Plus near Brawijaya Museum</t>
+          <t>Everyday Smart Hotel Malang</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>313066</v>
+        <v>309517</v>
       </c>
       <c r="E11" t="n">
-        <v>313066</v>
+        <v>309517</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Masjid Agung Jami' Kota Malang</t>
+          <t>Hawai Waterpark</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>150000</v>
+        <v>85000</v>
       </c>
       <c r="H11" t="n">
-        <v>150000</v>
+        <v>85000</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Pondok Desa</t>
+          <t>Depot Shanghai</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>35000</v>
+        <v>34000</v>
       </c>
       <c r="K11" t="n">
-        <v>210000</v>
+        <v>204000</v>
       </c>
       <c r="L11" t="n">
-        <v>4.34</v>
+        <v>13.99</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1215,16 +1215,16 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>9762</v>
+        <v>31489</v>
       </c>
       <c r="O11" t="n">
-        <v>682828</v>
+        <v>630006</v>
       </c>
       <c r="P11" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q11" t="n">
-        <v>4317172</v>
+        <v>369994</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1246,39 +1246,39 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>The Grand Palace Hotel Malang</t>
+          <t>Everyday Smart Hotel Malang</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>318189</v>
+        <v>309517</v>
       </c>
       <c r="E12" t="n">
-        <v>318189</v>
+        <v>309517</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Masjid Agung Jami' Kota Malang</t>
+          <t>Hawai Waterpark</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>150000</v>
+        <v>85000</v>
       </c>
       <c r="H12" t="n">
-        <v>150000</v>
+        <v>85000</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Melati Restaurant</t>
+          <t>Hot Cui Mie</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>36000</v>
+        <v>32250</v>
       </c>
       <c r="K12" t="n">
-        <v>216000</v>
+        <v>193500</v>
       </c>
       <c r="L12" t="n">
-        <v>2.56</v>
+        <v>15.11</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1286,16 +1286,16 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>5763</v>
+        <v>33988</v>
       </c>
       <c r="O12" t="n">
-        <v>689952</v>
+        <v>622005</v>
       </c>
       <c r="P12" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q12" t="n">
-        <v>4310048</v>
+        <v>377995</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1317,39 +1317,39 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>The Grand Palace Hotel Malang</t>
+          <t>Merbabu Guest House</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>318189</v>
+        <v>307698</v>
       </c>
       <c r="E13" t="n">
-        <v>318189</v>
+        <v>307698</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sweetmemoriesselfie</t>
+          <t>Hawai Waterpark</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>170000</v>
+        <v>85000</v>
       </c>
       <c r="H13" t="n">
-        <v>170000</v>
+        <v>85000</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Melati Restaurant</t>
+          <t>Hot Cui Mie</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>36000</v>
+        <v>32250</v>
       </c>
       <c r="K13" t="n">
-        <v>216000</v>
+        <v>193500</v>
       </c>
       <c r="L13" t="n">
-        <v>2.72</v>
+        <v>15.53</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1357,16 +1357,16 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>6125</v>
+        <v>34937</v>
       </c>
       <c r="O13" t="n">
-        <v>710314</v>
+        <v>621135</v>
       </c>
       <c r="P13" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q13" t="n">
-        <v>4289686</v>
+        <v>378865</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1388,39 +1388,39 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Merbabu Guest House</t>
+          <t>Se.nandung Living &amp; Space</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>307698</v>
+        <v>320000</v>
       </c>
       <c r="E14" t="n">
-        <v>307698</v>
+        <v>320000</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Masjid Agung Jami' Kota Malang</t>
+          <t>Hawai Waterpark</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>150000</v>
+        <v>85000</v>
       </c>
       <c r="H14" t="n">
-        <v>150000</v>
+        <v>85000</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Pondok Desa</t>
+          <t>Depot Shanghai</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>35000</v>
+        <v>34000</v>
       </c>
       <c r="K14" t="n">
-        <v>210000</v>
+        <v>204000</v>
       </c>
       <c r="L14" t="n">
-        <v>4.94</v>
+        <v>15.63</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>11111</v>
+        <v>35169</v>
       </c>
       <c r="O14" t="n">
-        <v>678809</v>
+        <v>644169</v>
       </c>
       <c r="P14" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q14" t="n">
-        <v>4321191</v>
+        <v>355831</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1459,39 +1459,39 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RedDoorz Plus near Brawijaya Museum</t>
+          <t>Merbabu Guest House</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>313066</v>
+        <v>307698</v>
       </c>
       <c r="E15" t="n">
-        <v>313066</v>
+        <v>307698</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sweetmemoriesselfie</t>
+          <t>Hawai Waterpark</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>170000</v>
+        <v>85000</v>
       </c>
       <c r="H15" t="n">
-        <v>170000</v>
+        <v>85000</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Pondok Desa</t>
+          <t>Depot Shanghai</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>35000</v>
+        <v>34000</v>
       </c>
       <c r="K15" t="n">
-        <v>210000</v>
+        <v>204000</v>
       </c>
       <c r="L15" t="n">
-        <v>5.15</v>
+        <v>15.85</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1499,16 +1499,16 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>11588</v>
+        <v>35671</v>
       </c>
       <c r="O15" t="n">
-        <v>704654</v>
+        <v>632369</v>
       </c>
       <c r="P15" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q15" t="n">
-        <v>4295346</v>
+        <v>367631</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -1530,39 +1530,39 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Merbabu Guest House</t>
+          <t>Se.nandung Living &amp; Space</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>307698</v>
+        <v>320000</v>
       </c>
       <c r="E16" t="n">
-        <v>307698</v>
+        <v>320000</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sweetmemoriesselfie</t>
+          <t>Hawai Waterpark</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>170000</v>
+        <v>85000</v>
       </c>
       <c r="H16" t="n">
-        <v>170000</v>
+        <v>85000</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Pondok Desa</t>
+          <t>Hot Cui Mie</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>35000</v>
+        <v>32250</v>
       </c>
       <c r="K16" t="n">
-        <v>210000</v>
+        <v>193500</v>
       </c>
       <c r="L16" t="n">
-        <v>5.65</v>
+        <v>16.99</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1570,16 +1570,16 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>12719</v>
+        <v>38222</v>
       </c>
       <c r="O16" t="n">
-        <v>700417</v>
+        <v>636722</v>
       </c>
       <c r="P16" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q16" t="n">
-        <v>4299583</v>
+        <v>363278</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -1601,39 +1601,39 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lembah Metro Resort</t>
+          <t>Hotel Grand Cakra</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1982645</v>
+        <v>533836</v>
       </c>
       <c r="E17" t="n">
-        <v>1982645</v>
+        <v>533836</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Offroad Coban Talun - Offroad Batu Malang</t>
+          <t>BatuPaintball</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>300000</v>
+        <v>130000</v>
       </c>
       <c r="H17" t="n">
-        <v>300000</v>
+        <v>130000</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>DEDUWA OLEH OLEH RESTO DAN TRANSIT</t>
+          <t>Depot Rawon Malang MM</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>150000</v>
+        <v>44500</v>
       </c>
       <c r="K17" t="n">
-        <v>900000</v>
+        <v>267000</v>
       </c>
       <c r="L17" t="n">
-        <v>19.66</v>
+        <v>29.97</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>44225</v>
+        <v>67430</v>
       </c>
       <c r="O17" t="n">
-        <v>3226870</v>
+        <v>998266</v>
       </c>
       <c r="P17" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q17" t="n">
-        <v>1773130</v>
+        <v>1734</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -1672,39 +1672,39 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lembah Metro Resort</t>
+          <t>The Batu Hotel &amp; Villas</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1982645</v>
+        <v>525487</v>
       </c>
       <c r="E18" t="n">
-        <v>1982645</v>
+        <v>525487</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Offroad Coban Talun - Offroad Batu Malang</t>
+          <t>BatuPaintball</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>300000</v>
+        <v>130000</v>
       </c>
       <c r="H18" t="n">
-        <v>300000</v>
+        <v>130000</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>De Bamboo Restaurant</t>
+          <t>A-yem Tiamkopi</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>51182</v>
+        <v>49665</v>
       </c>
       <c r="K18" t="n">
-        <v>307092</v>
+        <v>297990</v>
       </c>
       <c r="L18" t="n">
-        <v>19.72</v>
+        <v>16.23</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>44364</v>
+        <v>36524</v>
       </c>
       <c r="O18" t="n">
-        <v>2634101</v>
+        <v>990001</v>
       </c>
       <c r="P18" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q18" t="n">
-        <v>2365899</v>
+        <v>9999</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -1743,39 +1743,39 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lembah Metro Resort</t>
+          <t>Senyum World Hotel</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1982645</v>
+        <v>540000</v>
       </c>
       <c r="E19" t="n">
-        <v>1982645</v>
+        <v>540000</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Offroad Coban Talun - Offroad Batu Malang</t>
+          <t>Batu Secret Zoo</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>300000</v>
+        <v>125000</v>
       </c>
       <c r="H19" t="n">
-        <v>300000</v>
+        <v>125000</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
+          <t>A-yem Tiamkopi</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>68500</v>
+        <v>49665</v>
       </c>
       <c r="K19" t="n">
-        <v>411000</v>
+        <v>297990</v>
       </c>
       <c r="L19" t="n">
-        <v>20.81</v>
+        <v>15.41</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1783,16 +1783,16 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>46832</v>
+        <v>34682</v>
       </c>
       <c r="O19" t="n">
-        <v>2740477</v>
+        <v>997672</v>
       </c>
       <c r="P19" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q19" t="n">
-        <v>2259523</v>
+        <v>2328</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>

--- a/SIMULATION/EXPERIMENT MODEL/START/rekomendasi_paket.xlsx
+++ b/SIMULATION/EXPERIMENT MODEL/START/rekomendasi_paket.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,39 +536,39 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>OYO 1194 Villa Bukit Panderman Residence</t>
+          <t>Family Homestay Arya</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>182484</v>
+        <v>220925</v>
       </c>
       <c r="E2" t="n">
-        <v>182484</v>
+        <v>220925</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kusuma Waterpark</t>
+          <t>Kapal Nabi Nuh</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="H2" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Kedai Kopi Mbok gandul tujinem</t>
+          <t>Rawon Subuh Makmur</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>19000</v>
+        <v>20000</v>
       </c>
       <c r="K2" t="n">
-        <v>114000</v>
+        <v>120000</v>
       </c>
       <c r="L2" t="n">
-        <v>5.64</v>
+        <v>2.53</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>12689</v>
+        <v>5699</v>
       </c>
       <c r="O2" t="n">
-        <v>334173</v>
+        <v>396624</v>
       </c>
       <c r="P2" t="n">
         <v>1000000</v>
       </c>
       <c r="Q2" t="n">
-        <v>665827</v>
+        <v>603376</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -607,39 +607,39 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OYO 1194 Villa Bukit Panderman Residence</t>
+          <t>Hotel Prima Asri 153</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>182484</v>
+        <v>219000</v>
       </c>
       <c r="E3" t="n">
-        <v>182484</v>
+        <v>219000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kusuma Edukasi Pertanian</t>
+          <t>Kota Wisata Batu Jawa Timur</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="H3" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Kedai Kopi Mbok gandul tujinem</t>
+          <t>Warung Luweng Pedes</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>19000</v>
+        <v>20000</v>
       </c>
       <c r="K3" t="n">
-        <v>114000</v>
+        <v>120000</v>
       </c>
       <c r="L3" t="n">
-        <v>5.96</v>
+        <v>3.04</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -647,16 +647,16 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>13406</v>
+        <v>6849</v>
       </c>
       <c r="O3" t="n">
-        <v>334890</v>
+        <v>395849</v>
       </c>
       <c r="P3" t="n">
         <v>1000000</v>
       </c>
       <c r="Q3" t="n">
-        <v>665110</v>
+        <v>604151</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -678,39 +678,39 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kahan Homestay</t>
+          <t>Family Homestay Arya</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>176740</v>
+        <v>220925</v>
       </c>
       <c r="E4" t="n">
-        <v>176740</v>
+        <v>220925</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kusuma Waterpark</t>
+          <t>Eco Active Park</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="H4" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Kedai Kopi Mbok gandul tujinem</t>
+          <t>Rawon Subuh Makmur</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>19000</v>
+        <v>20000</v>
       </c>
       <c r="K4" t="n">
-        <v>114000</v>
+        <v>120000</v>
       </c>
       <c r="L4" t="n">
-        <v>8.220000000000001</v>
+        <v>3.13</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -718,16 +718,16 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>18497</v>
+        <v>7035</v>
       </c>
       <c r="O4" t="n">
-        <v>334237</v>
+        <v>397960</v>
       </c>
       <c r="P4" t="n">
         <v>1000000</v>
       </c>
       <c r="Q4" t="n">
-        <v>665763</v>
+        <v>602040</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -749,39 +749,39 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Super OYO 604 Cemara's Homestay</t>
+          <t>Hotel Prima Asri 153</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>182496</v>
+        <v>219000</v>
       </c>
       <c r="E5" t="n">
-        <v>182496</v>
+        <v>219000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kusuma Waterpark</t>
+          <t>Eco Active Park</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="H5" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Kedai Kopi Mbok gandul tujinem</t>
+          <t>Warung Luweng Pedes</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>19000</v>
+        <v>20000</v>
       </c>
       <c r="K5" t="n">
-        <v>114000</v>
+        <v>120000</v>
       </c>
       <c r="L5" t="n">
-        <v>8.470000000000001</v>
+        <v>3.29</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -789,16 +789,16 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>19068</v>
+        <v>7414</v>
       </c>
       <c r="O5" t="n">
-        <v>340564</v>
+        <v>396414</v>
       </c>
       <c r="P5" t="n">
         <v>1000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>659436</v>
+        <v>603586</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -820,39 +820,39 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kahan Homestay</t>
+          <t>Hotel Prima Asri 153</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>176740</v>
+        <v>219000</v>
       </c>
       <c r="E6" t="n">
-        <v>176740</v>
+        <v>219000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kusuma Edukasi Pertanian</t>
+          <t>Kota Wisata Batu Jawa Timur</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="H6" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Kedai Kopi Mbok gandul tujinem</t>
+          <t>Depot Harapan</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>19000</v>
+        <v>20000</v>
       </c>
       <c r="K6" t="n">
-        <v>114000</v>
+        <v>120000</v>
       </c>
       <c r="L6" t="n">
-        <v>8.57</v>
+        <v>3.33</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -860,16 +860,16 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>19287</v>
+        <v>7499</v>
       </c>
       <c r="O6" t="n">
-        <v>335027</v>
+        <v>396499</v>
       </c>
       <c r="P6" t="n">
         <v>1000000</v>
       </c>
       <c r="Q6" t="n">
-        <v>664973</v>
+        <v>603501</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -883,7 +883,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BALANCED</t>
+          <t>PREMIUM</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -891,39 +891,39 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>D'Fresh Guest House and Resto</t>
+          <t>Hotel Grand Cakra</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>327600</v>
+        <v>533836</v>
       </c>
       <c r="E7" t="n">
-        <v>327600</v>
+        <v>533836</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
+          <t>BatuPaintball</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>85000</v>
+        <v>130000</v>
       </c>
       <c r="H7" t="n">
-        <v>85000</v>
+        <v>130000</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Depot Shanghai</t>
+          <t>Depot Rawon Malang MM</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>34000</v>
+        <v>44500</v>
       </c>
       <c r="K7" t="n">
-        <v>204000</v>
+        <v>267000</v>
       </c>
       <c r="L7" t="n">
-        <v>8.42</v>
+        <v>29.97</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>18939</v>
+        <v>67430</v>
       </c>
       <c r="O7" t="n">
-        <v>635539</v>
+        <v>998266</v>
       </c>
       <c r="P7" t="n">
         <v>1000000</v>
       </c>
       <c r="Q7" t="n">
-        <v>364461</v>
+        <v>1734</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -954,7 +954,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BALANCED</t>
+          <t>PREMIUM</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -962,39 +962,39 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hotel Grage Malang</t>
+          <t>The Batu Hotel &amp; Villas</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>315315</v>
+        <v>525487</v>
       </c>
       <c r="E8" t="n">
-        <v>315315</v>
+        <v>525487</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
+          <t>BatuPaintball</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>85000</v>
+        <v>130000</v>
       </c>
       <c r="H8" t="n">
-        <v>85000</v>
+        <v>130000</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Depot Shanghai</t>
+          <t>A-yem Tiamkopi</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>34000</v>
+        <v>49665</v>
       </c>
       <c r="K8" t="n">
-        <v>204000</v>
+        <v>297990</v>
       </c>
       <c r="L8" t="n">
-        <v>10.49</v>
+        <v>16.23</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>23598</v>
+        <v>36524</v>
       </c>
       <c r="O8" t="n">
-        <v>627913</v>
+        <v>990001</v>
       </c>
       <c r="P8" t="n">
         <v>1000000</v>
       </c>
       <c r="Q8" t="n">
-        <v>372087</v>
+        <v>9999</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BALANCED</t>
+          <t>PREMIUM</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1033,39 +1033,39 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>D'Fresh Guest House and Resto</t>
+          <t>Senyum World Hotel</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>327600</v>
+        <v>540000</v>
       </c>
       <c r="E9" t="n">
-        <v>327600</v>
+        <v>540000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
+          <t>Batu Secret Zoo</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>85000</v>
+        <v>125000</v>
       </c>
       <c r="H9" t="n">
-        <v>85000</v>
+        <v>125000</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Hot Cui Mie</t>
+          <t>A-yem Tiamkopi</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>32250</v>
+        <v>49665</v>
       </c>
       <c r="K9" t="n">
-        <v>193500</v>
+        <v>297990</v>
       </c>
       <c r="L9" t="n">
-        <v>10.91</v>
+        <v>15.41</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>24546</v>
+        <v>34682</v>
       </c>
       <c r="O9" t="n">
-        <v>630646</v>
+        <v>997672</v>
       </c>
       <c r="P9" t="n">
         <v>1000000</v>
       </c>
       <c r="Q9" t="n">
-        <v>369354</v>
+        <v>2328</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1096,7 +1096,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BALANCED</t>
+          <t>PREMIUM</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1104,39 +1104,39 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hotel Grage Malang</t>
+          <t>The Batu Hotel &amp; Villas</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>315315</v>
+        <v>525487</v>
       </c>
       <c r="E10" t="n">
-        <v>315315</v>
+        <v>525487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
+          <t>Batu Secret Zoo</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>85000</v>
+        <v>125000</v>
       </c>
       <c r="H10" t="n">
-        <v>85000</v>
+        <v>125000</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Hot Cui Mie</t>
+          <t>A-yem Tiamkopi</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>32250</v>
+        <v>49665</v>
       </c>
       <c r="K10" t="n">
-        <v>193500</v>
+        <v>297990</v>
       </c>
       <c r="L10" t="n">
-        <v>13.51</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1144,16 +1144,16 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>30396</v>
+        <v>19188</v>
       </c>
       <c r="O10" t="n">
-        <v>624211</v>
+        <v>967665</v>
       </c>
       <c r="P10" t="n">
         <v>1000000</v>
       </c>
       <c r="Q10" t="n">
-        <v>375789</v>
+        <v>32335</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1167,7 +1167,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BALANCED</t>
+          <t>PREMIUM</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1175,39 +1175,39 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Everyday Smart Hotel Malang</t>
+          <t>The Batu Hotel &amp; Villas</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>309517</v>
+        <v>525487</v>
       </c>
       <c r="E11" t="n">
-        <v>309517</v>
+        <v>525487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
+          <t>Museum Satwa Jawa Timur Park 2</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>85000</v>
+        <v>140000</v>
       </c>
       <c r="H11" t="n">
-        <v>85000</v>
+        <v>140000</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Depot Shanghai</t>
+          <t>A-yem Tiamkopi</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>34000</v>
+        <v>49665</v>
       </c>
       <c r="K11" t="n">
-        <v>204000</v>
+        <v>297990</v>
       </c>
       <c r="L11" t="n">
-        <v>13.99</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1215,589 +1215,21 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>31489</v>
+        <v>19384</v>
       </c>
       <c r="O11" t="n">
-        <v>630006</v>
+        <v>982861</v>
       </c>
       <c r="P11" t="n">
         <v>1000000</v>
       </c>
       <c r="Q11" t="n">
-        <v>369994</v>
+        <v>17139</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>BALANCED</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>6</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Everyday Smart Hotel Malang</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>309517</v>
-      </c>
-      <c r="E12" t="n">
-        <v>309517</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Hawai Waterpark</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="H12" t="n">
-        <v>85000</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Hot Cui Mie</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>32250</v>
-      </c>
-      <c r="K12" t="n">
-        <v>193500</v>
-      </c>
-      <c r="L12" t="n">
-        <v>15.11</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>33988</v>
-      </c>
-      <c r="O12" t="n">
-        <v>622005</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>377995</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>BALANCED</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>7</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Merbabu Guest House</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>307698</v>
-      </c>
-      <c r="E13" t="n">
-        <v>307698</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Hawai Waterpark</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>85000</v>
-      </c>
-      <c r="H13" t="n">
-        <v>85000</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Hot Cui Mie</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>32250</v>
-      </c>
-      <c r="K13" t="n">
-        <v>193500</v>
-      </c>
-      <c r="L13" t="n">
-        <v>15.53</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
-        <v>34937</v>
-      </c>
-      <c r="O13" t="n">
-        <v>621135</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>378865</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>BALANCED</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>8</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Se.nandung Living &amp; Space</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>320000</v>
-      </c>
-      <c r="E14" t="n">
-        <v>320000</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Hawai Waterpark</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>85000</v>
-      </c>
-      <c r="H14" t="n">
-        <v>85000</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Depot Shanghai</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>34000</v>
-      </c>
-      <c r="K14" t="n">
-        <v>204000</v>
-      </c>
-      <c r="L14" t="n">
-        <v>15.63</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
-      </c>
-      <c r="N14" t="n">
-        <v>35169</v>
-      </c>
-      <c r="O14" t="n">
-        <v>644169</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>355831</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>BALANCED</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>9</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Merbabu Guest House</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>307698</v>
-      </c>
-      <c r="E15" t="n">
-        <v>307698</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Hawai Waterpark</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>85000</v>
-      </c>
-      <c r="H15" t="n">
-        <v>85000</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Depot Shanghai</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>34000</v>
-      </c>
-      <c r="K15" t="n">
-        <v>204000</v>
-      </c>
-      <c r="L15" t="n">
-        <v>15.85</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>35671</v>
-      </c>
-      <c r="O15" t="n">
-        <v>632369</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>367631</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>BALANCED</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>10</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Se.nandung Living &amp; Space</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>320000</v>
-      </c>
-      <c r="E16" t="n">
-        <v>320000</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Hawai Waterpark</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>85000</v>
-      </c>
-      <c r="H16" t="n">
-        <v>85000</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Hot Cui Mie</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>32250</v>
-      </c>
-      <c r="K16" t="n">
-        <v>193500</v>
-      </c>
-      <c r="L16" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
-        <v>38222</v>
-      </c>
-      <c r="O16" t="n">
-        <v>636722</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>363278</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>PREMIUM</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Hotel Grand Cakra</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>533836</v>
-      </c>
-      <c r="E17" t="n">
-        <v>533836</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>BatuPaintball</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>130000</v>
-      </c>
-      <c r="H17" t="n">
-        <v>130000</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Depot Rawon Malang MM</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>44500</v>
-      </c>
-      <c r="K17" t="n">
-        <v>267000</v>
-      </c>
-      <c r="L17" t="n">
-        <v>29.97</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
-      </c>
-      <c r="N17" t="n">
-        <v>67430</v>
-      </c>
-      <c r="O17" t="n">
-        <v>998266</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1734</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>PREMIUM</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>The Batu Hotel &amp; Villas</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>525487</v>
-      </c>
-      <c r="E18" t="n">
-        <v>525487</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>BatuPaintball</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>130000</v>
-      </c>
-      <c r="H18" t="n">
-        <v>130000</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>A-yem Tiamkopi</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>49665</v>
-      </c>
-      <c r="K18" t="n">
-        <v>297990</v>
-      </c>
-      <c r="L18" t="n">
-        <v>16.23</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
-      </c>
-      <c r="N18" t="n">
-        <v>36524</v>
-      </c>
-      <c r="O18" t="n">
-        <v>990001</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>9999</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>PREMIUM</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Senyum World Hotel</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>540000</v>
-      </c>
-      <c r="E19" t="n">
-        <v>540000</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Batu Secret Zoo</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>125000</v>
-      </c>
-      <c r="H19" t="n">
-        <v>125000</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>A-yem Tiamkopi</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>49665</v>
-      </c>
-      <c r="K19" t="n">
-        <v>297990</v>
-      </c>
-      <c r="L19" t="n">
-        <v>15.41</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>34682</v>
-      </c>
-      <c r="O19" t="n">
-        <v>997672</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2328</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>

--- a/SIMULATION/EXPERIMENT MODEL/START/rekomendasi_paket.xlsx
+++ b/SIMULATION/EXPERIMENT MODEL/START/rekomendasi_paket.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,56 +536,56 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Family Homestay Arya</t>
+          <t>Mustika Sari Hotel</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>220925</v>
+        <v>114825</v>
       </c>
       <c r="E2" t="n">
-        <v>220925</v>
+        <v>114825</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kapal Nabi Nuh</t>
+          <t>wisata petik jeruk super agro kota batu</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="H2" t="n">
         <v>50000</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Rawon Subuh Makmur</t>
+          <t>Kopi Sontoloyo</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>20000</v>
+        <v>5500</v>
       </c>
       <c r="K2" t="n">
-        <v>120000</v>
+        <v>66000</v>
       </c>
       <c r="L2" t="n">
-        <v>2.53</v>
+        <v>6.08</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Motor GoRide (1 orang)</t>
+          <t>Mobil GoCar Standard (2-4 orang)</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>5699</v>
+        <v>31324</v>
       </c>
       <c r="O2" t="n">
-        <v>396624</v>
+        <v>262149</v>
       </c>
       <c r="P2" t="n">
-        <v>1000000</v>
+        <v>510000</v>
       </c>
       <c r="Q2" t="n">
-        <v>603376</v>
+        <v>247851</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -607,56 +607,56 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>Mustika Sari Hotel</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>219000</v>
+        <v>114825</v>
       </c>
       <c r="E3" t="n">
-        <v>219000</v>
+        <v>114825</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kota Wisata Batu Jawa Timur</t>
+          <t>Petik apel malang &amp; petik jeruk keprok "BATU AGRO APEL" kota batu, malang</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="H3" t="n">
         <v>50000</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Warung Luweng Pedes</t>
+          <t>Kopi Sontoloyo</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>20000</v>
+        <v>5500</v>
       </c>
       <c r="K3" t="n">
-        <v>120000</v>
+        <v>66000</v>
       </c>
       <c r="L3" t="n">
-        <v>3.04</v>
+        <v>6.22</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Motor GoRide (1 orang)</t>
+          <t>Mobil GoCar Standard (2-4 orang)</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>6849</v>
+        <v>32050</v>
       </c>
       <c r="O3" t="n">
-        <v>395849</v>
+        <v>262875</v>
       </c>
       <c r="P3" t="n">
-        <v>1000000</v>
+        <v>510000</v>
       </c>
       <c r="Q3" t="n">
-        <v>604151</v>
+        <v>247125</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -678,56 +678,56 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Family Homestay Arya</t>
+          <t>Mustika Sari Hotel</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>220925</v>
+        <v>114825</v>
       </c>
       <c r="E4" t="n">
-        <v>220925</v>
+        <v>114825</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Eco Active Park</t>
+          <t>Petik Apel Green Garden</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="H4" t="n">
         <v>50000</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Rawon Subuh Makmur</t>
+          <t>Kopi Sontoloyo</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>20000</v>
+        <v>5500</v>
       </c>
       <c r="K4" t="n">
-        <v>120000</v>
+        <v>66000</v>
       </c>
       <c r="L4" t="n">
-        <v>3.13</v>
+        <v>6.88</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Motor GoRide (1 orang)</t>
+          <t>Mobil GoCar Standard (2-4 orang)</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7035</v>
+        <v>35426</v>
       </c>
       <c r="O4" t="n">
-        <v>397960</v>
+        <v>266251</v>
       </c>
       <c r="P4" t="n">
-        <v>1000000</v>
+        <v>510000</v>
       </c>
       <c r="Q4" t="n">
-        <v>602040</v>
+        <v>243749</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -749,56 +749,56 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>RedDoorz Syariah near Batu Night Spectacular 3</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>219000</v>
+        <v>115851</v>
       </c>
       <c r="E5" t="n">
-        <v>219000</v>
+        <v>115851</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eco Active Park</t>
+          <t>Batu Economis Park</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>50000</v>
+        <v>24750</v>
       </c>
       <c r="H5" t="n">
-        <v>50000</v>
+        <v>49500</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Warung Luweng Pedes</t>
+          <t>Bakso Pak Waji</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="K5" t="n">
-        <v>120000</v>
+        <v>72000</v>
       </c>
       <c r="L5" t="n">
-        <v>3.29</v>
+        <v>7.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Motor GoRide (1 orang)</t>
+          <t>Mobil GoCar Standard (2-4 orang)</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>7414</v>
+        <v>37611</v>
       </c>
       <c r="O5" t="n">
-        <v>396414</v>
+        <v>274962</v>
       </c>
       <c r="P5" t="n">
-        <v>1000000</v>
+        <v>510000</v>
       </c>
       <c r="Q5" t="n">
-        <v>603586</v>
+        <v>235038</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -820,56 +820,56 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hotel Prima Asri 153</t>
+          <t>RedDoorz Syariah near Batu Night Spectacular</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>219000</v>
+        <v>115851</v>
       </c>
       <c r="E6" t="n">
-        <v>219000</v>
+        <v>115851</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kota Wisata Batu Jawa Timur</t>
+          <t>Batu Economis Park</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>50000</v>
+        <v>24750</v>
       </c>
       <c r="H6" t="n">
-        <v>50000</v>
+        <v>49500</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Depot Harapan</t>
+          <t>Bakso Pak Waji</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="K6" t="n">
-        <v>120000</v>
+        <v>72000</v>
       </c>
       <c r="L6" t="n">
-        <v>3.33</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Motor GoRide (1 orang)</t>
+          <t>Mobil GoCar Standard (2-4 orang)</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>7499</v>
+        <v>41871</v>
       </c>
       <c r="O6" t="n">
-        <v>396499</v>
+        <v>279222</v>
       </c>
       <c r="P6" t="n">
-        <v>1000000</v>
+        <v>510000</v>
       </c>
       <c r="Q6" t="n">
-        <v>603501</v>
+        <v>230778</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -883,7 +883,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>BALANCED</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -891,63 +891,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hotel Grand Cakra</t>
+          <t>Griya Sumber Rejeki Homestay</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>533836</v>
+        <v>205648</v>
       </c>
       <c r="E7" t="n">
-        <v>533836</v>
+        <v>205648</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BatuPaintball</t>
+          <t>Museum D'Topeng Kingdom (INDONESIAN HERITAGE MUSEUM) Jatim Park 1</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>130000</v>
+        <v>39600</v>
       </c>
       <c r="H7" t="n">
-        <v>130000</v>
+        <v>79200</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Depot Rawon Malang MM</t>
+          <t>JM Steak and Milk Kota Batu</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>44500</v>
+        <v>19432</v>
       </c>
       <c r="K7" t="n">
-        <v>267000</v>
+        <v>233184</v>
       </c>
       <c r="L7" t="n">
-        <v>29.97</v>
+        <v>5.37</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Motor GoRide (1 orang)</t>
+          <t>Mobil GoCar Standard (2-4 orang)</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>67430</v>
+        <v>27660</v>
       </c>
       <c r="O7" t="n">
-        <v>998266</v>
+        <v>545692</v>
       </c>
       <c r="P7" t="n">
-        <v>1000000</v>
+        <v>510000</v>
       </c>
       <c r="Q7" t="n">
-        <v>1734</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>35692</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>UNDER BUDGET</t>
+          <t>OVER BUDGET</t>
         </is>
       </c>
     </row>
@@ -958,280 +958,67 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>The Batu Hotel &amp; Villas</t>
+          <t>Urbanview Hotel Bubusini Batu</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>525487</v>
+        <v>338695</v>
       </c>
       <c r="E8" t="n">
-        <v>525487</v>
+        <v>338695</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BatuPaintball</t>
+          <t>Batu Secret Zoo</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>130000</v>
+        <v>125000</v>
       </c>
       <c r="H8" t="n">
-        <v>130000</v>
+        <v>250000</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>A-yem Tiamkopi</t>
+          <t>Gubug asape Asapan dan bakaran</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>49665</v>
+        <v>37800</v>
       </c>
       <c r="K8" t="n">
-        <v>297990</v>
+        <v>453600</v>
       </c>
       <c r="L8" t="n">
-        <v>16.23</v>
+        <v>7.58</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Motor GoRide (1 orang)</t>
+          <t>Mobil GoCar Standard (2-4 orang)</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>36524</v>
+        <v>39017</v>
       </c>
       <c r="O8" t="n">
-        <v>990001</v>
+        <v>1081312</v>
       </c>
       <c r="P8" t="n">
-        <v>1000000</v>
+        <v>510000</v>
       </c>
       <c r="Q8" t="n">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>571312</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>UNDER BUDGET</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>PREMIUM</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Senyum World Hotel</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>540000</v>
-      </c>
-      <c r="E9" t="n">
-        <v>540000</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Batu Secret Zoo</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>125000</v>
-      </c>
-      <c r="H9" t="n">
-        <v>125000</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>A-yem Tiamkopi</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>49665</v>
-      </c>
-      <c r="K9" t="n">
-        <v>297990</v>
-      </c>
-      <c r="L9" t="n">
-        <v>15.41</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>34682</v>
-      </c>
-      <c r="O9" t="n">
-        <v>997672</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2328</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>PREMIUM</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>4</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>The Batu Hotel &amp; Villas</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>525487</v>
-      </c>
-      <c r="E10" t="n">
-        <v>525487</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Batu Secret Zoo</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>125000</v>
-      </c>
-      <c r="H10" t="n">
-        <v>125000</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>A-yem Tiamkopi</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>49665</v>
-      </c>
-      <c r="K10" t="n">
-        <v>297990</v>
-      </c>
-      <c r="L10" t="n">
-        <v>8.529999999999999</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>19188</v>
-      </c>
-      <c r="O10" t="n">
-        <v>967665</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>32335</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>PREMIUM</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>The Batu Hotel &amp; Villas</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>525487</v>
-      </c>
-      <c r="E11" t="n">
-        <v>525487</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Museum Satwa Jawa Timur Park 2</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>140000</v>
-      </c>
-      <c r="H11" t="n">
-        <v>140000</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>A-yem Tiamkopi</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>49665</v>
-      </c>
-      <c r="K11" t="n">
-        <v>297990</v>
-      </c>
-      <c r="L11" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>19384</v>
-      </c>
-      <c r="O11" t="n">
-        <v>982861</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>17139</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
+          <t>OVER BUDGET</t>
         </is>
       </c>
     </row>

--- a/SIMULATION/EXPERIMENT MODEL/START/rekomendasi_paket.xlsx
+++ b/SIMULATION/EXPERIMENT MODEL/START/rekomendasi_paket.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,56 +536,56 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mustika Sari Hotel</t>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>114825</v>
+        <v>182484</v>
       </c>
       <c r="E2" t="n">
-        <v>114825</v>
+        <v>182484</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>wisata petik jeruk super agro kota batu</t>
+          <t>Kusuma Waterpark</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>25000</v>
       </c>
       <c r="H2" t="n">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Kopi Sontoloyo</t>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5500</v>
+        <v>19000</v>
       </c>
       <c r="K2" t="n">
-        <v>66000</v>
+        <v>114000</v>
       </c>
       <c r="L2" t="n">
-        <v>6.08</v>
+        <v>5.64</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Mobil GoCar Standard (2-4 orang)</t>
+          <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>31324</v>
+        <v>12689</v>
       </c>
       <c r="O2" t="n">
-        <v>262149</v>
+        <v>334173</v>
       </c>
       <c r="P2" t="n">
-        <v>510000</v>
+        <v>1500000</v>
       </c>
       <c r="Q2" t="n">
-        <v>247851</v>
+        <v>1165827</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -607,56 +607,56 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mustika Sari Hotel</t>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>114825</v>
+        <v>182484</v>
       </c>
       <c r="E3" t="n">
-        <v>114825</v>
+        <v>182484</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Petik apel malang &amp; petik jeruk keprok "BATU AGRO APEL" kota batu, malang</t>
+          <t>Kusuma Edukasi Pertanian</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>25000</v>
       </c>
       <c r="H3" t="n">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Kopi Sontoloyo</t>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>5500</v>
+        <v>19000</v>
       </c>
       <c r="K3" t="n">
-        <v>66000</v>
+        <v>114000</v>
       </c>
       <c r="L3" t="n">
-        <v>6.22</v>
+        <v>5.96</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Mobil GoCar Standard (2-4 orang)</t>
+          <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>32050</v>
+        <v>13406</v>
       </c>
       <c r="O3" t="n">
-        <v>262875</v>
+        <v>334890</v>
       </c>
       <c r="P3" t="n">
-        <v>510000</v>
+        <v>1500000</v>
       </c>
       <c r="Q3" t="n">
-        <v>247125</v>
+        <v>1165110</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -678,56 +678,56 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mustika Sari Hotel</t>
+          <t>Kahan Homestay</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>114825</v>
+        <v>176740</v>
       </c>
       <c r="E4" t="n">
-        <v>114825</v>
+        <v>176740</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Petik Apel Green Garden</t>
+          <t>Kusuma Waterpark</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>25000</v>
       </c>
       <c r="H4" t="n">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Kopi Sontoloyo</t>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5500</v>
+        <v>19000</v>
       </c>
       <c r="K4" t="n">
-        <v>66000</v>
+        <v>114000</v>
       </c>
       <c r="L4" t="n">
-        <v>6.88</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Mobil GoCar Standard (2-4 orang)</t>
+          <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>35426</v>
+        <v>18497</v>
       </c>
       <c r="O4" t="n">
-        <v>266251</v>
+        <v>334237</v>
       </c>
       <c r="P4" t="n">
-        <v>510000</v>
+        <v>1500000</v>
       </c>
       <c r="Q4" t="n">
-        <v>243749</v>
+        <v>1165763</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -749,56 +749,56 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RedDoorz Syariah near Batu Night Spectacular 3</t>
+          <t>Super OYO 604 Cemara's Homestay</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>115851</v>
+        <v>182496</v>
       </c>
       <c r="E5" t="n">
-        <v>115851</v>
+        <v>182496</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Batu Economis Park</t>
+          <t>Kusuma Waterpark</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>24750</v>
+        <v>25000</v>
       </c>
       <c r="H5" t="n">
-        <v>49500</v>
+        <v>25000</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Bakso Pak Waji</t>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6000</v>
+        <v>19000</v>
       </c>
       <c r="K5" t="n">
-        <v>72000</v>
+        <v>114000</v>
       </c>
       <c r="L5" t="n">
-        <v>7.3</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Mobil GoCar Standard (2-4 orang)</t>
+          <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>37611</v>
+        <v>19068</v>
       </c>
       <c r="O5" t="n">
-        <v>274962</v>
+        <v>340564</v>
       </c>
       <c r="P5" t="n">
-        <v>510000</v>
+        <v>1500000</v>
       </c>
       <c r="Q5" t="n">
-        <v>235038</v>
+        <v>1159436</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -820,56 +820,56 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RedDoorz Syariah near Batu Night Spectacular</t>
+          <t>Kahan Homestay</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>115851</v>
+        <v>176740</v>
       </c>
       <c r="E6" t="n">
-        <v>115851</v>
+        <v>176740</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Batu Economis Park</t>
+          <t>Kusuma Edukasi Pertanian</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>24750</v>
+        <v>25000</v>
       </c>
       <c r="H6" t="n">
-        <v>49500</v>
+        <v>25000</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Bakso Pak Waji</t>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6000</v>
+        <v>19000</v>
       </c>
       <c r="K6" t="n">
-        <v>72000</v>
+        <v>114000</v>
       </c>
       <c r="L6" t="n">
-        <v>8.130000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Mobil GoCar Standard (2-4 orang)</t>
+          <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>41871</v>
+        <v>19287</v>
       </c>
       <c r="O6" t="n">
-        <v>279222</v>
+        <v>335027</v>
       </c>
       <c r="P6" t="n">
-        <v>510000</v>
+        <v>1500000</v>
       </c>
       <c r="Q6" t="n">
-        <v>230778</v>
+        <v>1164973</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -883,142 +883,2840 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BALANCED</t>
+          <t>HEMAT</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Griya Sumber Rejeki Homestay</t>
+          <t>Super OYO 604 Cemara's Homestay</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>205648</v>
+        <v>182496</v>
       </c>
       <c r="E7" t="n">
-        <v>205648</v>
+        <v>182496</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Museum D'Topeng Kingdom (INDONESIAN HERITAGE MUSEUM) Jatim Park 1</t>
+          <t>Kusuma Edukasi Pertanian</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>39600</v>
+        <v>25000</v>
       </c>
       <c r="H7" t="n">
-        <v>79200</v>
+        <v>25000</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>JM Steak and Milk Kota Batu</t>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>19432</v>
+        <v>19000</v>
       </c>
       <c r="K7" t="n">
-        <v>233184</v>
+        <v>114000</v>
       </c>
       <c r="L7" t="n">
-        <v>5.37</v>
+        <v>8.83</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Mobil GoCar Standard (2-4 orang)</t>
+          <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>27660</v>
+        <v>19862</v>
       </c>
       <c r="O7" t="n">
-        <v>545692</v>
+        <v>341358</v>
       </c>
       <c r="P7" t="n">
-        <v>510000</v>
+        <v>1500000</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1158642</v>
       </c>
       <c r="R7" t="n">
-        <v>35692</v>
+        <v>0</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>OVER BUDGET</t>
+          <t>UNDER BUDGET</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>HEMAT</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Super OYO 604 Cemara's Homestay</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>182496</v>
+      </c>
+      <c r="E8" t="n">
+        <v>182496</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Wisata Edukasi Susu Batu</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>114000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>23760</v>
+      </c>
+      <c r="O8" t="n">
+        <v>345256</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1154744</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HEMAT</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Kahan Homestay</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>176740</v>
+      </c>
+      <c r="E9" t="n">
+        <v>176740</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Wisata Edukasi Susu Batu</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>114000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>23919</v>
+      </c>
+      <c r="O9" t="n">
+        <v>339659</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1160341</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HEMAT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>RedDoorz Plus near Balai Kota Batu 2</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>180000</v>
+      </c>
+      <c r="E10" t="n">
+        <v>180000</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kusuma Edukasi Pertanian</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K10" t="n">
+        <v>114000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>24052</v>
+      </c>
+      <c r="O10" t="n">
+        <v>343052</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1156948</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HEMAT</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>RedDoorz Plus near Balai Kota Batu 2</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>180000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>180000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kusuma Waterpark</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K11" t="n">
+        <v>114000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>24080</v>
+      </c>
+      <c r="O11" t="n">
+        <v>343080</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1156920</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HEMAT</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SR Guesthouse</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>173966</v>
+      </c>
+      <c r="E12" t="n">
+        <v>173966</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kusuma Waterpark</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K12" t="n">
+        <v>114000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>24516</v>
+      </c>
+      <c r="O12" t="n">
+        <v>337482</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1162518</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HEMAT</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SR Guesthouse</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>173966</v>
+      </c>
+      <c r="E13" t="n">
+        <v>173966</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kusuma Edukasi Pertanian</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>114000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>24522</v>
+      </c>
+      <c r="O13" t="n">
+        <v>337488</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1162512</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HEMAT</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Kahan Homestay</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>176740</v>
+      </c>
+      <c r="E14" t="n">
+        <v>176740</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lumbung Stroberi Official</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K14" t="n">
+        <v>114000</v>
+      </c>
+      <c r="L14" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>26721</v>
+      </c>
+      <c r="O14" t="n">
+        <v>342461</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1157539</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HEMAT</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Super OYO 604 Cemara's Homestay</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>182496</v>
+      </c>
+      <c r="E15" t="n">
+        <v>182496</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lumbung Stroberi Official</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H15" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>114000</v>
+      </c>
+      <c r="L15" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>27169</v>
+      </c>
+      <c r="O15" t="n">
+        <v>348665</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1151335</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HEMAT</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>182484</v>
+      </c>
+      <c r="E16" t="n">
+        <v>182484</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lumbung Stroberi Official</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H16" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K16" t="n">
+        <v>114000</v>
+      </c>
+      <c r="L16" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>27746</v>
+      </c>
+      <c r="O16" t="n">
+        <v>349230</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1150770</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BALANCED</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>D'Fresh Guest House and Resto</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>327600</v>
+      </c>
+      <c r="E17" t="n">
+        <v>327600</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Hawai Waterpark</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H17" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>35385</v>
+      </c>
+      <c r="K17" t="n">
+        <v>212310</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>19094</v>
+      </c>
+      <c r="O17" t="n">
+        <v>644004</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>855996</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BALANCED</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>D'Fresh Guest House and Resto</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>327600</v>
+      </c>
+      <c r="E18" t="n">
+        <v>327600</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Hawai Waterpark</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H18" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Depot Shanghai</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>34000</v>
+      </c>
+      <c r="K18" t="n">
+        <v>204000</v>
+      </c>
+      <c r="L18" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>18939</v>
+      </c>
+      <c r="O18" t="n">
+        <v>635539</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>864461</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BALANCED</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Hotel Grage Malang</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>315315</v>
+      </c>
+      <c r="E19" t="n">
+        <v>315315</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Hawai Waterpark</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H19" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>35385</v>
+      </c>
+      <c r="K19" t="n">
+        <v>212310</v>
+      </c>
+      <c r="L19" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>24936</v>
+      </c>
+      <c r="O19" t="n">
+        <v>637561</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>862439</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BALANCED</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Semeru Hostel Malang</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>307162</v>
+      </c>
+      <c r="E20" t="n">
+        <v>307162</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Hawai Waterpark</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Pondok Desa</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>35000</v>
+      </c>
+      <c r="K20" t="n">
+        <v>210000</v>
+      </c>
+      <c r="L20" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>41359</v>
+      </c>
+      <c r="O20" t="n">
+        <v>643521</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>856479</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BALANCED</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Merbabu Guest House</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>307698</v>
+      </c>
+      <c r="E21" t="n">
+        <v>307698</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Hawai Waterpark</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pondok Desa</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>35000</v>
+      </c>
+      <c r="K21" t="n">
+        <v>210000</v>
+      </c>
+      <c r="L21" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>41433</v>
+      </c>
+      <c r="O21" t="n">
+        <v>644131</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>855869</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BALANCED</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>6</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Hotel Grage Malang</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>315315</v>
+      </c>
+      <c r="E22" t="n">
+        <v>315315</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Hawai Waterpark</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H22" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Depot Shanghai</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>34000</v>
+      </c>
+      <c r="K22" t="n">
+        <v>204000</v>
+      </c>
+      <c r="L22" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>23598</v>
+      </c>
+      <c r="O22" t="n">
+        <v>627913</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>872087</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BALANCED</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>D'Fresh Guest House and Resto</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>327600</v>
+      </c>
+      <c r="E23" t="n">
+        <v>327600</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Hawai Waterpark</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Pondok Desa</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>35000</v>
+      </c>
+      <c r="K23" t="n">
+        <v>210000</v>
+      </c>
+      <c r="L23" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>42611</v>
+      </c>
+      <c r="O23" t="n">
+        <v>665211</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>834789</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BALANCED</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>8</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>RedDoorz Plus near Brawijaya Museum</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>313066</v>
+      </c>
+      <c r="E24" t="n">
+        <v>313066</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Hawai Waterpark</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H24" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Pondok Desa</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>35000</v>
+      </c>
+      <c r="K24" t="n">
+        <v>210000</v>
+      </c>
+      <c r="L24" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>43499</v>
+      </c>
+      <c r="O24" t="n">
+        <v>651565</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>848435</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BALANCED</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>9</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Everyday Smart Hotel Malang</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>309517</v>
+      </c>
+      <c r="E25" t="n">
+        <v>309517</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Hawai Waterpark</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H25" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>35385</v>
+      </c>
+      <c r="K25" t="n">
+        <v>212310</v>
+      </c>
+      <c r="L25" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>31525</v>
+      </c>
+      <c r="O25" t="n">
+        <v>638352</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>861648</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BALANCED</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>10</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Merbabu Guest House</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>307698</v>
+      </c>
+      <c r="E26" t="n">
+        <v>307698</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Hawai Waterpark</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H26" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Melati Restaurant</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>36000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>216000</v>
+      </c>
+      <c r="L26" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>40605</v>
+      </c>
+      <c r="O26" t="n">
+        <v>649303</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>850697</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BALANCED</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>11</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>D'Fresh Guest House and Resto</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>327600</v>
+      </c>
+      <c r="E27" t="n">
+        <v>327600</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Hawai Waterpark</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Melati Restaurant</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>36000</v>
+      </c>
+      <c r="K27" t="n">
+        <v>216000</v>
+      </c>
+      <c r="L27" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>40830</v>
+      </c>
+      <c r="O27" t="n">
+        <v>669430</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>830570</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BALANCED</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>12</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Everyday Smart Hotel Malang</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>309517</v>
+      </c>
+      <c r="E28" t="n">
+        <v>309517</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Hawai Waterpark</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H28" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Pondok Desa</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>35000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>210000</v>
+      </c>
+      <c r="L28" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>45673</v>
+      </c>
+      <c r="O28" t="n">
+        <v>650190</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>849810</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BALANCED</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>13</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>The Grand Palace Hotel Malang</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>318189</v>
+      </c>
+      <c r="E29" t="n">
+        <v>318189</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Hawai Waterpark</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H29" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Pondok Desa</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>35000</v>
+      </c>
+      <c r="K29" t="n">
+        <v>210000</v>
+      </c>
+      <c r="L29" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>45822</v>
+      </c>
+      <c r="O29" t="n">
+        <v>659011</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>840989</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BALANCED</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>14</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Semeru Hostel Malang</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>307162</v>
+      </c>
+      <c r="E30" t="n">
+        <v>307162</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Hawai Waterpark</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H30" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Melati Restaurant</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>36000</v>
+      </c>
+      <c r="K30" t="n">
+        <v>216000</v>
+      </c>
+      <c r="L30" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>41748</v>
+      </c>
+      <c r="O30" t="n">
+        <v>649910</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>850090</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BALANCED</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>15</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>The Grand Palace Hotel Malang</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>318189</v>
+      </c>
+      <c r="E31" t="n">
+        <v>318189</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Hawai Waterpark</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H31" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Melati Restaurant</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>36000</v>
+      </c>
+      <c r="K31" t="n">
+        <v>216000</v>
+      </c>
+      <c r="L31" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>44159</v>
+      </c>
+      <c r="O31" t="n">
+        <v>663348</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>836652</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B32" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Urbanview Hotel Bubusini Batu</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>338695</v>
-      </c>
-      <c r="E8" t="n">
-        <v>338695</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Batu Secret Zoo</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>125000</v>
-      </c>
-      <c r="H8" t="n">
-        <v>250000</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Gubug asape Asapan dan bakaran</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>37800</v>
-      </c>
-      <c r="K8" t="n">
-        <v>453600</v>
-      </c>
-      <c r="L8" t="n">
-        <v>7.58</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Mobil GoCar Standard (2-4 orang)</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>39017</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1081312</v>
-      </c>
-      <c r="P8" t="n">
-        <v>510000</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>571312</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>OVER BUDGET</t>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sea Villa Kota Batu</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>130000</v>
+      </c>
+      <c r="H32" t="n">
+        <v>130000</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Kutaraja Boutique Restaurant</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>53500</v>
+      </c>
+      <c r="K32" t="n">
+        <v>321000</v>
+      </c>
+      <c r="L32" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>16258</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1467258</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>32742</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PREMIUM</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Sea Villa Kota Batu</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>130000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>130000</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>De Bamboo Restaurant</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>51182</v>
+      </c>
+      <c r="K33" t="n">
+        <v>307092</v>
+      </c>
+      <c r="L33" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>38695</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1475787</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>24213</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PREMIUM</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Bobocabin Coban Rondo, Malang</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>813000</v>
+      </c>
+      <c r="E34" t="n">
+        <v>813000</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>130000</v>
+      </c>
+      <c r="H34" t="n">
+        <v>130000</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Sop Janda Suroboyo - BATU MALANG</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>68500</v>
+      </c>
+      <c r="K34" t="n">
+        <v>411000</v>
+      </c>
+      <c r="L34" t="n">
+        <v>22.18</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>49900</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1403900</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>96100</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PREMIUM</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Bobocabin Coban Rondo, Malang</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>813000</v>
+      </c>
+      <c r="E35" t="n">
+        <v>813000</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>130000</v>
+      </c>
+      <c r="H35" t="n">
+        <v>130000</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>De Bamboo Restaurant</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>51182</v>
+      </c>
+      <c r="K35" t="n">
+        <v>307092</v>
+      </c>
+      <c r="L35" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>50238</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1300330</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>199670</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PREMIUM</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Bobocabin Coban Rondo, Malang</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>813000</v>
+      </c>
+      <c r="E36" t="n">
+        <v>813000</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>130000</v>
+      </c>
+      <c r="H36" t="n">
+        <v>130000</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Kutaraja Boutique Restaurant</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>53500</v>
+      </c>
+      <c r="K36" t="n">
+        <v>321000</v>
+      </c>
+      <c r="L36" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>50527</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1314527</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>185473</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PREMIUM</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>6</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Bobocabin Coban Rondo, Malang</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>813000</v>
+      </c>
+      <c r="E37" t="n">
+        <v>813000</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>130000</v>
+      </c>
+      <c r="H37" t="n">
+        <v>130000</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Warung Sate Gule Bang Tismanto</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>60000</v>
+      </c>
+      <c r="K37" t="n">
+        <v>360000</v>
+      </c>
+      <c r="L37" t="n">
+        <v>38.01</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>85530</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1388530</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>111470</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PREMIUM</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>7</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Bobocabin Coban Rondo, Malang</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>813000</v>
+      </c>
+      <c r="E38" t="n">
+        <v>813000</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>130000</v>
+      </c>
+      <c r="H38" t="n">
+        <v>130000</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>DAPUR LAWAS MALANG</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>58500</v>
+      </c>
+      <c r="K38" t="n">
+        <v>351000</v>
+      </c>
+      <c r="L38" t="n">
+        <v>46.29</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>104153</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1398153</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>101847</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PREMIUM</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>8</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Bobocabin Coban Rondo, Malang</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>813000</v>
+      </c>
+      <c r="E39" t="n">
+        <v>813000</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>130000</v>
+      </c>
+      <c r="H39" t="n">
+        <v>130000</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Depot Kanton</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>65000</v>
+      </c>
+      <c r="K39" t="n">
+        <v>390000</v>
+      </c>
+      <c r="L39" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>113144</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1446144</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>53856</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PREMIUM</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>9</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Bobocabin Coban Rondo, Malang</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>813000</v>
+      </c>
+      <c r="E40" t="n">
+        <v>813000</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>130000</v>
+      </c>
+      <c r="H40" t="n">
+        <v>130000</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Depot Widari</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>50600</v>
+      </c>
+      <c r="K40" t="n">
+        <v>303600</v>
+      </c>
+      <c r="L40" t="n">
+        <v>50.36</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>113311</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1359911</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>140089</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PREMIUM</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>10</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Bobocabin Coban Rondo, Malang</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>813000</v>
+      </c>
+      <c r="E41" t="n">
+        <v>813000</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>130000</v>
+      </c>
+      <c r="H41" t="n">
+        <v>130000</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Depot Santai</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K41" t="n">
+        <v>300000</v>
+      </c>
+      <c r="L41" t="n">
+        <v>50.54</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>113710</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1356710</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>143290</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PREMIUM</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>11</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Bobocabin Coban Rondo, Malang</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>813000</v>
+      </c>
+      <c r="E42" t="n">
+        <v>813000</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>130000</v>
+      </c>
+      <c r="H42" t="n">
+        <v>130000</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Depot Gang Djangkrik</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>65714</v>
+      </c>
+      <c r="K42" t="n">
+        <v>394284</v>
+      </c>
+      <c r="L42" t="n">
+        <v>50.84</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>114401</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1451685</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>48315</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PREMIUM</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>12</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Bobocabin Coban Rondo, Malang</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>813000</v>
+      </c>
+      <c r="E43" t="n">
+        <v>813000</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>130000</v>
+      </c>
+      <c r="H43" t="n">
+        <v>130000</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>55500</v>
+      </c>
+      <c r="K43" t="n">
+        <v>333000</v>
+      </c>
+      <c r="L43" t="n">
+        <v>51.02</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>114785</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1390785</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>109215</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PREMIUM</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>13</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Bobocabin Coban Rondo, Malang</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>813000</v>
+      </c>
+      <c r="E44" t="n">
+        <v>813000</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>130000</v>
+      </c>
+      <c r="H44" t="n">
+        <v>130000</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Veggie Kitchen Malang (Vegetarian Food)</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>55377</v>
+      </c>
+      <c r="K44" t="n">
+        <v>332262</v>
+      </c>
+      <c r="L44" t="n">
+        <v>51.31</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>115445</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1390707</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>109293</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PREMIUM</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>14</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Bobocabin Coban Rondo, Malang</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>813000</v>
+      </c>
+      <c r="E45" t="n">
+        <v>813000</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>130000</v>
+      </c>
+      <c r="H45" t="n">
+        <v>130000</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Depot 88 - Araya</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>58750</v>
+      </c>
+      <c r="K45" t="n">
+        <v>352500</v>
+      </c>
+      <c r="L45" t="n">
+        <v>54.02</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>121547</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1417047</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>82953</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PREMIUM</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>15</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Hotel Kawi Surapatha</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>800000</v>
+      </c>
+      <c r="E46" t="n">
+        <v>800000</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>BatuPaintball</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>130000</v>
+      </c>
+      <c r="H46" t="n">
+        <v>130000</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Kutaraja Boutique Restaurant</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>53500</v>
+      </c>
+      <c r="K46" t="n">
+        <v>321000</v>
+      </c>
+      <c r="L46" t="n">
+        <v>44.83</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>100875</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1351875</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>148125</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
         </is>
       </c>
     </row>

--- a/SIMULATION/EXPERIMENT MODEL/START/rekomendasi_paket.xlsx
+++ b/SIMULATION/EXPERIMENT MODEL/START/rekomendasi_paket.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rangkuman Opsi" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rincian Per Opsi" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S46"/>
+  <dimension ref="A1:U32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,55 +472,65 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Nama Kuliner</t>
+          <t>Nama Kuliner Siang</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Harga Kuliner (Porsi)</t>
+          <t>Harga Kuliner Siang</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Nama Kuliner Malam</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Harga Kuliner Malam</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Total Biaya Kuliner</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Rute Transport (Jarak km)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Armada Transport</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Biaya Transport</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Estimasi Total Biaya</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Total Budget Input</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Sisa Anggaran</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Kelebihan Anggaran</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -547,50 +558,58 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kusuma Waterpark</t>
+          <t>Taman Suko</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>25000</v>
+        <v>29000</v>
       </c>
       <c r="H2" t="n">
-        <v>25000</v>
+        <v>53500</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>WARUNG ENAK ECO BU KUSTIN</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>19000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>114000</v>
-      </c>
       <c r="L2" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="M2" t="inlineStr">
+        <v>19000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>95000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>12689</v>
-      </c>
-      <c r="O2" t="n">
-        <v>334173</v>
-      </c>
       <c r="P2" t="n">
+        <v>604291</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>935275</v>
+      </c>
+      <c r="R2" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1165827</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="S2" t="n">
+        <v>564725</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -618,50 +637,58 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kusuma Edukasi Pertanian</t>
+          <t>Taman Suko</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>25000</v>
+        <v>29000</v>
       </c>
       <c r="H3" t="n">
-        <v>25000</v>
+        <v>53500</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Warung Lalapan Mbak Denok</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>19000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>114000</v>
-      </c>
       <c r="L3" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="M3" t="inlineStr">
+        <v>19000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>95000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>13406</v>
-      </c>
-      <c r="O3" t="n">
-        <v>334890</v>
-      </c>
       <c r="P3" t="n">
+        <v>604291</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>935275</v>
+      </c>
+      <c r="R3" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1165110</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" t="n">
+        <v>564725</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -678,61 +705,69 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kahan Homestay</t>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>176740</v>
+        <v>182484</v>
       </c>
       <c r="E4" t="n">
-        <v>176740</v>
+        <v>182484</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kusuma Waterpark</t>
+          <t>Taman Suko</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>25000</v>
+        <v>29000</v>
       </c>
       <c r="H4" t="n">
-        <v>25000</v>
+        <v>53500</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Rumah Makan Padang SEDERHANA BARU</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>19000</v>
-      </c>
-      <c r="K4" t="n">
-        <v>114000</v>
-      </c>
       <c r="L4" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="M4" t="inlineStr">
+        <v>19000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>95000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v>18497</v>
-      </c>
-      <c r="O4" t="n">
-        <v>334237</v>
-      </c>
       <c r="P4" t="n">
+        <v>604291</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>935275</v>
+      </c>
+      <c r="R4" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1165763</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="S4" t="n">
+        <v>564725</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -749,61 +784,69 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Super OYO 604 Cemara's Homestay</t>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>182496</v>
+        <v>182484</v>
       </c>
       <c r="E5" t="n">
-        <v>182496</v>
+        <v>182484</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kusuma Waterpark</t>
+          <t>Taman Suko</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>25000</v>
+        <v>29000</v>
       </c>
       <c r="H5" t="n">
-        <v>25000</v>
+        <v>53500</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Depot Nik'mat</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>19000</v>
-      </c>
-      <c r="K5" t="n">
-        <v>114000</v>
-      </c>
       <c r="L5" t="n">
-        <v>8.470000000000001</v>
-      </c>
-      <c r="M5" t="inlineStr">
+        <v>19000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>95000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N5" t="n">
-        <v>19068</v>
-      </c>
-      <c r="O5" t="n">
-        <v>340564</v>
-      </c>
       <c r="P5" t="n">
+        <v>604291</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>935275</v>
+      </c>
+      <c r="R5" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1159436</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="S5" t="n">
+        <v>564725</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -820,25 +863,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kahan Homestay</t>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>176740</v>
+        <v>182484</v>
       </c>
       <c r="E6" t="n">
-        <v>176740</v>
+        <v>182484</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kusuma Edukasi Pertanian</t>
+          <t>Taman Suko</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>25000</v>
+        <v>29000</v>
       </c>
       <c r="H6" t="n">
-        <v>25000</v>
+        <v>53500</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -848,33 +891,41 @@
       <c r="J6" t="n">
         <v>19000</v>
       </c>
-      <c r="K6" t="n">
-        <v>114000</v>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Depot 200</t>
+        </is>
       </c>
       <c r="L6" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="M6" t="inlineStr">
+        <v>19000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>95000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N6" t="n">
-        <v>19287</v>
-      </c>
-      <c r="O6" t="n">
-        <v>335027</v>
-      </c>
       <c r="P6" t="n">
+        <v>604291</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>935275</v>
+      </c>
+      <c r="R6" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1164973</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="S6" t="n">
+        <v>564725</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -891,61 +942,69 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Super OYO 604 Cemara's Homestay</t>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>182496</v>
+        <v>182484</v>
       </c>
       <c r="E7" t="n">
-        <v>182496</v>
+        <v>182484</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kusuma Edukasi Pertanian</t>
+          <t>Taman Suko</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>25000</v>
+        <v>29000</v>
       </c>
       <c r="H7" t="n">
-        <v>25000</v>
+        <v>53500</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Makcik Pakcik Resto &amp; Cafe</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>19000</v>
-      </c>
-      <c r="K7" t="n">
-        <v>114000</v>
-      </c>
       <c r="L7" t="n">
-        <v>8.83</v>
-      </c>
-      <c r="M7" t="inlineStr">
+        <v>19000</v>
+      </c>
+      <c r="M7" t="n">
+        <v>95000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v>19862</v>
-      </c>
-      <c r="O7" t="n">
-        <v>341358</v>
-      </c>
       <c r="P7" t="n">
+        <v>604291</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>935275</v>
+      </c>
+      <c r="R7" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1158642</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="inlineStr">
+      <c r="S7" t="n">
+        <v>564725</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -962,61 +1021,69 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Super OYO 604 Cemara's Homestay</t>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>182496</v>
+        <v>182484</v>
       </c>
       <c r="E8" t="n">
-        <v>182496</v>
+        <v>182484</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wisata Edukasi Susu Batu</t>
+          <t>Taman Suko</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>25000</v>
+        <v>29000</v>
       </c>
       <c r="H8" t="n">
-        <v>25000</v>
+        <v>53500</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Warung Nasi Soto Gule Rawon Sawahan</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>19000</v>
-      </c>
-      <c r="K8" t="n">
-        <v>114000</v>
-      </c>
       <c r="L8" t="n">
-        <v>10.56</v>
-      </c>
-      <c r="M8" t="inlineStr">
+        <v>19000</v>
+      </c>
+      <c r="M8" t="n">
+        <v>95000</v>
+      </c>
+      <c r="N8" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>23760</v>
-      </c>
-      <c r="O8" t="n">
-        <v>345256</v>
-      </c>
       <c r="P8" t="n">
+        <v>604291</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>935275</v>
+      </c>
+      <c r="R8" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1154744</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="S8" t="n">
+        <v>564725</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1033,61 +1100,69 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kahan Homestay</t>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>176740</v>
+        <v>182484</v>
       </c>
       <c r="E9" t="n">
-        <v>176740</v>
+        <v>182484</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wisata Edukasi Susu Batu</t>
+          <t>Taman Suko</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>25000</v>
+        <v>29000</v>
       </c>
       <c r="H9" t="n">
-        <v>25000</v>
+        <v>53500</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Depot 200</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>19000</v>
-      </c>
-      <c r="K9" t="n">
-        <v>114000</v>
-      </c>
       <c r="L9" t="n">
-        <v>10.63</v>
-      </c>
-      <c r="M9" t="inlineStr">
+        <v>19000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>95000</v>
+      </c>
+      <c r="N9" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N9" t="n">
-        <v>23919</v>
-      </c>
-      <c r="O9" t="n">
-        <v>339659</v>
-      </c>
       <c r="P9" t="n">
+        <v>604291</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>935275</v>
+      </c>
+      <c r="R9" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1160341</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="S9" t="n">
+        <v>564725</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1104,61 +1179,69 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RedDoorz Plus near Balai Kota Batu 2</t>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>180000</v>
+        <v>182484</v>
       </c>
       <c r="E10" t="n">
-        <v>180000</v>
+        <v>182484</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kusuma Edukasi Pertanian</t>
+          <t>Taman Suko</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>25000</v>
+        <v>29000</v>
       </c>
       <c r="H10" t="n">
-        <v>25000</v>
+        <v>53500</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Bakso Mantap Cak Ba'un</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>19000</v>
-      </c>
-      <c r="K10" t="n">
-        <v>114000</v>
-      </c>
       <c r="L10" t="n">
-        <v>10.69</v>
-      </c>
-      <c r="M10" t="inlineStr">
+        <v>19000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>95000</v>
+      </c>
+      <c r="N10" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>24052</v>
-      </c>
-      <c r="O10" t="n">
-        <v>343052</v>
-      </c>
       <c r="P10" t="n">
+        <v>604291</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>935275</v>
+      </c>
+      <c r="R10" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1156948</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="S10" t="n">
+        <v>564725</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1175,61 +1258,69 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RedDoorz Plus near Balai Kota Batu 2</t>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>180000</v>
+        <v>182484</v>
       </c>
       <c r="E11" t="n">
-        <v>180000</v>
+        <v>182484</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kusuma Waterpark</t>
+          <t>Taman Suko</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>25000</v>
+        <v>29000</v>
       </c>
       <c r="H11" t="n">
-        <v>25000</v>
+        <v>53500</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Ayam Goreng Pak Maning</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>19000</v>
-      </c>
-      <c r="K11" t="n">
-        <v>114000</v>
-      </c>
       <c r="L11" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="M11" t="inlineStr">
+        <v>19000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>95000</v>
+      </c>
+      <c r="N11" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>24080</v>
-      </c>
-      <c r="O11" t="n">
-        <v>343080</v>
-      </c>
       <c r="P11" t="n">
+        <v>604291</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>935275</v>
+      </c>
+      <c r="R11" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q11" t="n">
-        <v>1156920</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="inlineStr">
+      <c r="S11" t="n">
+        <v>564725</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1246,61 +1337,69 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SR Guesthouse</t>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>173966</v>
+        <v>182484</v>
       </c>
       <c r="E12" t="n">
-        <v>173966</v>
+        <v>182484</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kusuma Waterpark</t>
+          <t>Taman Suko</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>25000</v>
+        <v>29000</v>
       </c>
       <c r="H12" t="n">
-        <v>25000</v>
+        <v>53500</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Warung Nasional 1</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>19000</v>
-      </c>
-      <c r="K12" t="n">
-        <v>114000</v>
-      </c>
       <c r="L12" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="M12" t="inlineStr">
+        <v>19000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>95000</v>
+      </c>
+      <c r="N12" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N12" t="n">
-        <v>24516</v>
-      </c>
-      <c r="O12" t="n">
-        <v>337482</v>
-      </c>
       <c r="P12" t="n">
+        <v>604291</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>935275</v>
+      </c>
+      <c r="R12" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q12" t="n">
-        <v>1162518</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr">
+      <c r="S12" t="n">
+        <v>564725</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1317,61 +1416,69 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SR Guesthouse</t>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>173966</v>
+        <v>182484</v>
       </c>
       <c r="E13" t="n">
-        <v>173966</v>
+        <v>182484</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kusuma Edukasi Pertanian</t>
+          <t>Taman Suko</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>25000</v>
+        <v>29000</v>
       </c>
       <c r="H13" t="n">
-        <v>25000</v>
+        <v>53500</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>Mitro Chinese Food</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>19000</v>
-      </c>
-      <c r="K13" t="n">
-        <v>114000</v>
-      </c>
       <c r="L13" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="M13" t="inlineStr">
+        <v>19000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>95000</v>
+      </c>
+      <c r="N13" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N13" t="n">
-        <v>24522</v>
-      </c>
-      <c r="O13" t="n">
-        <v>337488</v>
-      </c>
       <c r="P13" t="n">
+        <v>604291</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>935275</v>
+      </c>
+      <c r="R13" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1162512</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr">
+      <c r="S13" t="n">
+        <v>564725</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1388,61 +1495,69 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kahan Homestay</t>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>176740</v>
+        <v>182484</v>
       </c>
       <c r="E14" t="n">
-        <v>176740</v>
+        <v>182484</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lumbung Stroberi Official</t>
+          <t>Taman Suko</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>25000</v>
+        <v>29000</v>
       </c>
       <c r="H14" t="n">
-        <v>25000</v>
+        <v>53500</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>Depot Nikmat 2</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>19000</v>
-      </c>
-      <c r="K14" t="n">
-        <v>114000</v>
-      </c>
       <c r="L14" t="n">
-        <v>11.88</v>
-      </c>
-      <c r="M14" t="inlineStr">
+        <v>19000</v>
+      </c>
+      <c r="M14" t="n">
+        <v>95000</v>
+      </c>
+      <c r="N14" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N14" t="n">
-        <v>26721</v>
-      </c>
-      <c r="O14" t="n">
-        <v>342461</v>
-      </c>
       <c r="P14" t="n">
+        <v>604291</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>935275</v>
+      </c>
+      <c r="R14" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q14" t="n">
-        <v>1157539</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="inlineStr">
+      <c r="S14" t="n">
+        <v>564725</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1459,61 +1574,69 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Super OYO 604 Cemara's Homestay</t>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>182496</v>
+        <v>182484</v>
       </c>
       <c r="E15" t="n">
-        <v>182496</v>
+        <v>182484</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lumbung Stroberi Official</t>
+          <t>Taman Suko</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>25000</v>
+        <v>29000</v>
       </c>
       <c r="H15" t="n">
-        <v>25000</v>
+        <v>53500</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>Chicken Pingsaw</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>19000</v>
-      </c>
-      <c r="K15" t="n">
-        <v>114000</v>
-      </c>
       <c r="L15" t="n">
-        <v>12.07</v>
-      </c>
-      <c r="M15" t="inlineStr">
+        <v>19000</v>
+      </c>
+      <c r="M15" t="n">
+        <v>95000</v>
+      </c>
+      <c r="N15" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N15" t="n">
-        <v>27169</v>
-      </c>
-      <c r="O15" t="n">
-        <v>348665</v>
-      </c>
       <c r="P15" t="n">
+        <v>604291</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>935275</v>
+      </c>
+      <c r="R15" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1151335</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="inlineStr">
+      <c r="S15" t="n">
+        <v>564725</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1541,50 +1664,58 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lumbung Stroberi Official</t>
+          <t>Taman Suko</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>25000</v>
+        <v>29000</v>
       </c>
       <c r="H16" t="n">
-        <v>25000</v>
+        <v>53500</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>Bebek Bakar Bandar Lor</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>18800</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>Kedai Kopi Mbok gandul tujinem</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v>19000</v>
-      </c>
-      <c r="K16" t="n">
-        <v>114000</v>
-      </c>
       <c r="L16" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="M16" t="inlineStr">
+        <v>19000</v>
+      </c>
+      <c r="M16" t="n">
+        <v>95000</v>
+      </c>
+      <c r="N16" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N16" t="n">
-        <v>27746</v>
-      </c>
-      <c r="O16" t="n">
-        <v>349230</v>
-      </c>
       <c r="P16" t="n">
+        <v>604291</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>935275</v>
+      </c>
+      <c r="R16" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1150770</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="inlineStr">
+      <c r="S16" t="n">
+        <v>564725</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1612,50 +1743,58 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
+          <t>Muara Paradise</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>85000</v>
+        <v>75000</v>
       </c>
       <c r="H17" t="n">
-        <v>85000</v>
+        <v>179100</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>Pondok Desa</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>35000</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>Depot 2 Legenda</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>35385</v>
       </c>
-      <c r="K17" t="n">
-        <v>212310</v>
-      </c>
-      <c r="L17" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="M17" t="n">
+        <v>176770</v>
+      </c>
+      <c r="N17" t="n">
+        <v>64</v>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N17" t="n">
-        <v>19094</v>
-      </c>
-      <c r="O17" t="n">
-        <v>644004</v>
-      </c>
       <c r="P17" t="n">
+        <v>143992</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>827462</v>
+      </c>
+      <c r="R17" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q17" t="n">
-        <v>855996</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="inlineStr">
+      <c r="S17" t="n">
+        <v>672538</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1683,50 +1822,58 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
+          <t>Muara Paradise</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>85000</v>
+        <v>75000</v>
       </c>
       <c r="H18" t="n">
-        <v>85000</v>
+        <v>179100</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Depot Shanghai</t>
+          <t>Depot Nank Garasi</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>34000</v>
-      </c>
-      <c r="K18" t="n">
-        <v>204000</v>
+        <v>36018</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
       </c>
       <c r="L18" t="n">
-        <v>8.42</v>
-      </c>
-      <c r="M18" t="inlineStr">
+        <v>35385</v>
+      </c>
+      <c r="M18" t="n">
+        <v>176770</v>
+      </c>
+      <c r="N18" t="n">
+        <v>64</v>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N18" t="n">
-        <v>18939</v>
-      </c>
-      <c r="O18" t="n">
-        <v>635539</v>
-      </c>
       <c r="P18" t="n">
+        <v>143992</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>827462</v>
+      </c>
+      <c r="R18" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q18" t="n">
-        <v>864461</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="inlineStr">
+      <c r="S18" t="n">
+        <v>672538</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1743,61 +1890,69 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hotel Grage Malang</t>
+          <t>D'Fresh Guest House and Resto</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>315315</v>
+        <v>327600</v>
       </c>
       <c r="E19" t="n">
-        <v>315315</v>
+        <v>327600</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
+          <t>Muara Paradise</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>85000</v>
+        <v>75000</v>
       </c>
       <c r="H19" t="n">
-        <v>85000</v>
+        <v>179100</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>Melati Restaurant</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>36000</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>Depot 2 Legenda</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>35385</v>
       </c>
-      <c r="K19" t="n">
-        <v>212310</v>
-      </c>
-      <c r="L19" t="n">
-        <v>11.08</v>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="M19" t="n">
+        <v>176770</v>
+      </c>
+      <c r="N19" t="n">
+        <v>64</v>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N19" t="n">
-        <v>24936</v>
-      </c>
-      <c r="O19" t="n">
-        <v>637561</v>
-      </c>
       <c r="P19" t="n">
+        <v>143992</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>827462</v>
+      </c>
+      <c r="R19" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q19" t="n">
-        <v>862439</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="inlineStr">
+      <c r="S19" t="n">
+        <v>672538</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1814,61 +1969,69 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Semeru Hostel Malang</t>
+          <t>D'Fresh Guest House and Resto</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>307162</v>
+        <v>327600</v>
       </c>
       <c r="E20" t="n">
-        <v>307162</v>
+        <v>327600</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
+          <t>Muara Paradise</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>85000</v>
+        <v>75000</v>
       </c>
       <c r="H20" t="n">
-        <v>85000</v>
+        <v>179100</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Pondok Desa</t>
+          <t>DEPOT MAMAKU AYAM GORENG DAN NASI TIMBEL</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>35000</v>
-      </c>
-      <c r="K20" t="n">
-        <v>210000</v>
+        <v>35900</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
       </c>
       <c r="L20" t="n">
-        <v>18.38</v>
-      </c>
-      <c r="M20" t="inlineStr">
+        <v>35385</v>
+      </c>
+      <c r="M20" t="n">
+        <v>176770</v>
+      </c>
+      <c r="N20" t="n">
+        <v>64</v>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N20" t="n">
-        <v>41359</v>
-      </c>
-      <c r="O20" t="n">
-        <v>643521</v>
-      </c>
       <c r="P20" t="n">
+        <v>143992</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>827462</v>
+      </c>
+      <c r="R20" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q20" t="n">
-        <v>856479</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="inlineStr">
+      <c r="S20" t="n">
+        <v>672538</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1885,61 +2048,69 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Merbabu Guest House</t>
+          <t>D'Fresh Guest House and Resto</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>307698</v>
+        <v>327600</v>
       </c>
       <c r="E21" t="n">
-        <v>307698</v>
+        <v>327600</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
+          <t>Muara Paradise</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>85000</v>
+        <v>75000</v>
       </c>
       <c r="H21" t="n">
-        <v>85000</v>
+        <v>179100</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Pondok Desa</t>
+          <t>Gubug bromo</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>35000</v>
       </c>
-      <c r="K21" t="n">
-        <v>210000</v>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
       </c>
       <c r="L21" t="n">
-        <v>18.41</v>
-      </c>
-      <c r="M21" t="inlineStr">
+        <v>35385</v>
+      </c>
+      <c r="M21" t="n">
+        <v>176770</v>
+      </c>
+      <c r="N21" t="n">
+        <v>64</v>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N21" t="n">
-        <v>41433</v>
-      </c>
-      <c r="O21" t="n">
-        <v>644131</v>
-      </c>
       <c r="P21" t="n">
+        <v>143992</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>827462</v>
+      </c>
+      <c r="R21" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q21" t="n">
-        <v>855869</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="inlineStr">
+      <c r="S21" t="n">
+        <v>672538</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -1956,61 +2127,69 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hotel Grage Malang</t>
+          <t>Semeru Hostel Malang</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>315315</v>
+        <v>307162</v>
       </c>
       <c r="E22" t="n">
-        <v>315315</v>
+        <v>307162</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
+          <t>Muara Paradise</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>85000</v>
+        <v>75000</v>
       </c>
       <c r="H22" t="n">
-        <v>85000</v>
+        <v>179100</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Depot Shanghai</t>
+          <t>Pondok Desa</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>34000</v>
-      </c>
-      <c r="K22" t="n">
-        <v>204000</v>
+        <v>35000</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Melati Restaurant</t>
+        </is>
       </c>
       <c r="L22" t="n">
-        <v>10.49</v>
-      </c>
-      <c r="M22" t="inlineStr">
+        <v>36000</v>
+      </c>
+      <c r="M22" t="n">
+        <v>178018</v>
+      </c>
+      <c r="N22" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N22" t="n">
-        <v>23598</v>
-      </c>
-      <c r="O22" t="n">
-        <v>627913</v>
-      </c>
       <c r="P22" t="n">
+        <v>155698</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>819978</v>
+      </c>
+      <c r="R22" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q22" t="n">
-        <v>872087</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="inlineStr">
+      <c r="S22" t="n">
+        <v>680022</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -2027,25 +2206,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>D'Fresh Guest House and Resto</t>
+          <t>RedDoorz Plus near Brawijaya Museum</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>327600</v>
+        <v>313066</v>
       </c>
       <c r="E23" t="n">
-        <v>327600</v>
+        <v>313066</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
+          <t>Muara Paradise</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>85000</v>
+        <v>75000</v>
       </c>
       <c r="H23" t="n">
-        <v>85000</v>
+        <v>179100</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2055,33 +2234,41 @@
       <c r="J23" t="n">
         <v>35000</v>
       </c>
-      <c r="K23" t="n">
-        <v>210000</v>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Depot Nank Garasi</t>
+        </is>
       </c>
       <c r="L23" t="n">
-        <v>18.94</v>
-      </c>
-      <c r="M23" t="inlineStr">
+        <v>36018</v>
+      </c>
+      <c r="M23" t="n">
+        <v>179036</v>
+      </c>
+      <c r="N23" t="n">
+        <v>69.45</v>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N23" t="n">
-        <v>42611</v>
-      </c>
-      <c r="O23" t="n">
-        <v>665211</v>
-      </c>
       <c r="P23" t="n">
+        <v>156268</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>827470</v>
+      </c>
+      <c r="R23" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q23" t="n">
-        <v>834789</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="inlineStr">
+      <c r="S23" t="n">
+        <v>672530</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -2098,61 +2285,69 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RedDoorz Plus near Brawijaya Museum</t>
+          <t>D'Fresh Guest House and Resto</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>313066</v>
+        <v>327600</v>
       </c>
       <c r="E24" t="n">
-        <v>313066</v>
+        <v>327600</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
+          <t>Muara Paradise</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>85000</v>
+        <v>75000</v>
       </c>
       <c r="H24" t="n">
-        <v>85000</v>
+        <v>179100</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Pondok Desa</t>
+          <t>Depot 2 Legenda</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>35000</v>
-      </c>
-      <c r="K24" t="n">
-        <v>210000</v>
+        <v>35385</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Depot Shanghai</t>
+        </is>
       </c>
       <c r="L24" t="n">
-        <v>19.33</v>
-      </c>
-      <c r="M24" t="inlineStr">
+        <v>34000</v>
+      </c>
+      <c r="M24" t="n">
+        <v>176770</v>
+      </c>
+      <c r="N24" t="n">
+        <v>64</v>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N24" t="n">
-        <v>43499</v>
-      </c>
-      <c r="O24" t="n">
-        <v>651565</v>
-      </c>
       <c r="P24" t="n">
+        <v>143992</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>827462</v>
+      </c>
+      <c r="R24" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q24" t="n">
-        <v>848435</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="inlineStr">
+      <c r="S24" t="n">
+        <v>672538</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -2169,61 +2364,69 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Everyday Smart Hotel Malang</t>
+          <t>D'Fresh Guest House and Resto</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>309517</v>
+        <v>327600</v>
       </c>
       <c r="E25" t="n">
-        <v>309517</v>
+        <v>327600</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
+          <t>Muara Paradise</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>85000</v>
+        <v>75000</v>
       </c>
       <c r="H25" t="n">
-        <v>85000</v>
+        <v>179100</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>Rawon Nguling</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>34400</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>Depot 2 Legenda</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>35385</v>
       </c>
-      <c r="K25" t="n">
-        <v>212310</v>
-      </c>
-      <c r="L25" t="n">
-        <v>14.01</v>
-      </c>
-      <c r="M25" t="inlineStr">
+      <c r="M25" t="n">
+        <v>176770</v>
+      </c>
+      <c r="N25" t="n">
+        <v>64</v>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N25" t="n">
-        <v>31525</v>
-      </c>
-      <c r="O25" t="n">
-        <v>638352</v>
-      </c>
       <c r="P25" t="n">
+        <v>143992</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>827462</v>
+      </c>
+      <c r="R25" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q25" t="n">
-        <v>861648</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="inlineStr">
+      <c r="S25" t="n">
+        <v>672538</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -2240,61 +2443,69 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Merbabu Guest House</t>
+          <t>D'Fresh Guest House and Resto</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>307698</v>
+        <v>327600</v>
       </c>
       <c r="E26" t="n">
-        <v>307698</v>
+        <v>327600</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
+          <t>Muara Paradise</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>85000</v>
+        <v>75000</v>
       </c>
       <c r="H26" t="n">
-        <v>85000</v>
+        <v>179100</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Melati Restaurant</t>
+          <t>Ayam Goreng Pemuda</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>36000</v>
-      </c>
-      <c r="K26" t="n">
-        <v>216000</v>
+        <v>33750</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
       </c>
       <c r="L26" t="n">
-        <v>18.05</v>
-      </c>
-      <c r="M26" t="inlineStr">
+        <v>35385</v>
+      </c>
+      <c r="M26" t="n">
+        <v>176770</v>
+      </c>
+      <c r="N26" t="n">
+        <v>64</v>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N26" t="n">
-        <v>40605</v>
-      </c>
-      <c r="O26" t="n">
-        <v>649303</v>
-      </c>
       <c r="P26" t="n">
+        <v>143992</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>827462</v>
+      </c>
+      <c r="R26" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q26" t="n">
-        <v>850697</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="inlineStr">
+      <c r="S26" t="n">
+        <v>672538</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -2311,61 +2522,69 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>D'Fresh Guest House and Resto</t>
+          <t>The Grand Palace Hotel Malang</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>327600</v>
+        <v>318189</v>
       </c>
       <c r="E27" t="n">
-        <v>327600</v>
+        <v>318189</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
+          <t>Muara Paradise</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>85000</v>
+        <v>75000</v>
       </c>
       <c r="H27" t="n">
-        <v>85000</v>
+        <v>179100</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Melati Restaurant</t>
+          <t>Pondok Desa</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>36000</v>
-      </c>
-      <c r="K27" t="n">
-        <v>216000</v>
+        <v>35000</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Rawon Nguling</t>
+        </is>
       </c>
       <c r="L27" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="M27" t="inlineStr">
+        <v>34400</v>
+      </c>
+      <c r="M27" t="n">
+        <v>175800</v>
+      </c>
+      <c r="N27" t="n">
+        <v>70.31999999999999</v>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N27" t="n">
-        <v>40830</v>
-      </c>
-      <c r="O27" t="n">
-        <v>669430</v>
-      </c>
       <c r="P27" t="n">
+        <v>158212</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>831301</v>
+      </c>
+      <c r="R27" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q27" t="n">
-        <v>830570</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="inlineStr">
+      <c r="S27" t="n">
+        <v>668699</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -2382,61 +2601,69 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Everyday Smart Hotel Malang</t>
+          <t>Semeru Hostel Malang</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>309517</v>
+        <v>307162</v>
       </c>
       <c r="E28" t="n">
-        <v>309517</v>
+        <v>307162</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
+          <t>Muara Paradise</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>85000</v>
+        <v>75000</v>
       </c>
       <c r="H28" t="n">
-        <v>85000</v>
+        <v>179100</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
+          <t>Depot Nank Garasi</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>36018</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>Pondok Desa</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>35000</v>
       </c>
-      <c r="K28" t="n">
-        <v>210000</v>
-      </c>
-      <c r="L28" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="M28" t="inlineStr">
+      <c r="M28" t="n">
+        <v>178018</v>
+      </c>
+      <c r="N28" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N28" t="n">
-        <v>45673</v>
-      </c>
-      <c r="O28" t="n">
-        <v>650190</v>
-      </c>
       <c r="P28" t="n">
+        <v>155698</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>819978</v>
+      </c>
+      <c r="R28" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q28" t="n">
-        <v>849810</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="inlineStr">
+      <c r="S28" t="n">
+        <v>680022</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -2453,61 +2680,69 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>The Grand Palace Hotel Malang</t>
+          <t>Semeru Hostel Malang</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>318189</v>
+        <v>307162</v>
       </c>
       <c r="E29" t="n">
-        <v>318189</v>
+        <v>307162</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
+          <t>Muara Paradise</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>85000</v>
+        <v>75000</v>
       </c>
       <c r="H29" t="n">
-        <v>85000</v>
+        <v>179100</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
+          <t>Melati Restaurant</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>36000</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>Pondok Desa</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>35000</v>
       </c>
-      <c r="K29" t="n">
-        <v>210000</v>
-      </c>
-      <c r="L29" t="n">
-        <v>20.37</v>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="M29" t="n">
+        <v>178018</v>
+      </c>
+      <c r="N29" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N29" t="n">
-        <v>45822</v>
-      </c>
-      <c r="O29" t="n">
-        <v>659011</v>
-      </c>
       <c r="P29" t="n">
+        <v>155698</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>819978</v>
+      </c>
+      <c r="R29" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q29" t="n">
-        <v>840989</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="inlineStr">
+      <c r="S29" t="n">
+        <v>680022</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -2524,61 +2759,69 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Semeru Hostel Malang</t>
+          <t>Everyday Smart Hotel Malang</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>307162</v>
+        <v>309517</v>
       </c>
       <c r="E30" t="n">
-        <v>307162</v>
+        <v>309517</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
+          <t>Muara Paradise</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>85000</v>
+        <v>75000</v>
       </c>
       <c r="H30" t="n">
-        <v>85000</v>
+        <v>179100</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Melati Restaurant</t>
+          <t>Pondok Desa</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>36000</v>
-      </c>
-      <c r="K30" t="n">
-        <v>216000</v>
+        <v>35000</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
       </c>
       <c r="L30" t="n">
-        <v>18.55</v>
-      </c>
-      <c r="M30" t="inlineStr">
+        <v>35385</v>
+      </c>
+      <c r="M30" t="n">
+        <v>176770</v>
+      </c>
+      <c r="N30" t="n">
+        <v>71.45</v>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N30" t="n">
-        <v>41748</v>
-      </c>
-      <c r="O30" t="n">
-        <v>649910</v>
-      </c>
       <c r="P30" t="n">
+        <v>160766</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>826153</v>
+      </c>
+      <c r="R30" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q30" t="n">
-        <v>850090</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="inlineStr">
+      <c r="S30" t="n">
+        <v>673847</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -2595,61 +2838,69 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>The Grand Palace Hotel Malang</t>
+          <t>RedDoorz Plus near Brawijaya Museum</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>318189</v>
+        <v>313066</v>
       </c>
       <c r="E31" t="n">
-        <v>318189</v>
+        <v>313066</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hawai Waterpark</t>
+          <t>Muara Paradise</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>85000</v>
+        <v>75000</v>
       </c>
       <c r="H31" t="n">
-        <v>85000</v>
+        <v>179100</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Melati Restaurant</t>
+          <t>Depot Nank Garasi</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>36000</v>
-      </c>
-      <c r="K31" t="n">
-        <v>216000</v>
+        <v>36018</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Pondok Desa</t>
+        </is>
       </c>
       <c r="L31" t="n">
-        <v>19.63</v>
-      </c>
-      <c r="M31" t="inlineStr">
+        <v>35000</v>
+      </c>
+      <c r="M31" t="n">
+        <v>179036</v>
+      </c>
+      <c r="N31" t="n">
+        <v>69.45</v>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>Motor GoRide (1 orang)</t>
         </is>
       </c>
-      <c r="N31" t="n">
-        <v>44159</v>
-      </c>
-      <c r="O31" t="n">
-        <v>663348</v>
-      </c>
       <c r="P31" t="n">
+        <v>156268</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>827470</v>
+      </c>
+      <c r="R31" t="n">
         <v>1500000</v>
       </c>
-      <c r="Q31" t="n">
-        <v>836652</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="inlineStr">
+      <c r="S31" t="n">
+        <v>672530</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="inlineStr">
         <is>
           <t>UNDER BUDGET</t>
         </is>
@@ -2666,1058 +2917,5830 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sea Villa Kota Batu</t>
+          <t>Hotel Kawi Surapatha</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="E32" t="n">
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>BatuPaintball</t>
+          <t>Pujon Adventure &amp; Rafting</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>130000</v>
+        <v>275000</v>
       </c>
       <c r="H32" t="n">
-        <v>130000</v>
+        <v>395000</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Kutaraja Boutique Restaurant</t>
+          <t>Depot 59</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>53500</v>
-      </c>
-      <c r="K32" t="n">
-        <v>321000</v>
+        <v>95000</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Warung Sate Gule Bang Tismanto</t>
+        </is>
       </c>
       <c r="L32" t="n">
-        <v>7.23</v>
+        <v>60000</v>
+      </c>
+      <c r="M32" t="n">
+        <v>333877</v>
+      </c>
+      <c r="N32" t="n">
+        <v>122.59</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Motor GoRide (1 orang)</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>275817</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1804694</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>304694</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>OVER BUDGET</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Komponen / Rincian</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>HEMAT - OPSI 1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>HEMAT - OPSI 2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>HEMAT - OPSI 3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>HEMAT - OPSI 4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>HEMAT - OPSI 5</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>HEMAT - OPSI 6</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>HEMAT - OPSI 7</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>HEMAT - OPSI 8</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>HEMAT - OPSI 9</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>HEMAT - OPSI 10</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>HEMAT - OPSI 11</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>HEMAT - OPSI 12</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>HEMAT - OPSI 13</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>HEMAT - OPSI 14</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>HEMAT - OPSI 15</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>BALANCED - OPSI 1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>BALANCED - OPSI 2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>BALANCED - OPSI 3</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>BALANCED - OPSI 4</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>BALANCED - OPSI 5</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>BALANCED - OPSI 6</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>BALANCED - OPSI 7</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>BALANCED - OPSI 8</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>BALANCED - OPSI 9</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>BALANCED - OPSI 10</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>BALANCED - OPSI 11</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>BALANCED - OPSI 12</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>BALANCED - OPSI 13</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>BALANCED - OPSI 14</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>BALANCED - OPSI 15</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>PREMIUM - OPSI 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>UNDER BUDGET</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>OVER BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Hari 1: Hotel</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>OYO 1194 Villa Bukit Panderman Residence</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>D'Fresh Guest House and Resto</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>D'Fresh Guest House and Resto</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>D'Fresh Guest House and Resto</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>D'Fresh Guest House and Resto</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>D'Fresh Guest House and Resto</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Semeru Hostel Malang</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>RedDoorz Plus near Brawijaya Museum</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D'Fresh Guest House and Resto</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>D'Fresh Guest House and Resto</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>D'Fresh Guest House and Resto</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>The Grand Palace Hotel Malang</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Semeru Hostel Malang</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Semeru Hostel Malang</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Everyday Smart Hotel Malang</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>RedDoorz Plus near Brawijaya Museum</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Hotel Kawi Surapatha</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Hari 1: Harga Hotel (Satuan)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>182484</v>
+      </c>
+      <c r="C4" t="n">
+        <v>182484</v>
+      </c>
+      <c r="D4" t="n">
+        <v>182484</v>
+      </c>
+      <c r="E4" t="n">
+        <v>182484</v>
+      </c>
+      <c r="F4" t="n">
+        <v>182484</v>
+      </c>
+      <c r="G4" t="n">
+        <v>182484</v>
+      </c>
+      <c r="H4" t="n">
+        <v>182484</v>
+      </c>
+      <c r="I4" t="n">
+        <v>182484</v>
+      </c>
+      <c r="J4" t="n">
+        <v>182484</v>
+      </c>
+      <c r="K4" t="n">
+        <v>182484</v>
+      </c>
+      <c r="L4" t="n">
+        <v>182484</v>
+      </c>
+      <c r="M4" t="n">
+        <v>182484</v>
+      </c>
+      <c r="N4" t="n">
+        <v>182484</v>
+      </c>
+      <c r="O4" t="n">
+        <v>182484</v>
+      </c>
+      <c r="P4" t="n">
+        <v>182484</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>327600</v>
+      </c>
+      <c r="R4" t="n">
+        <v>327600</v>
+      </c>
+      <c r="S4" t="n">
+        <v>327600</v>
+      </c>
+      <c r="T4" t="n">
+        <v>327600</v>
+      </c>
+      <c r="U4" t="n">
+        <v>327600</v>
+      </c>
+      <c r="V4" t="n">
+        <v>307162</v>
+      </c>
+      <c r="W4" t="n">
+        <v>313066</v>
+      </c>
+      <c r="X4" t="n">
+        <v>327600</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>327600</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>327600</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>318189</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>307162</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>307162</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>309517</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>313066</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Hari 1: Wisata</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bukit Nando</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bukit Nando</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Bukit Nando</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bukit Nando</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bukit Nando</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bukit Nando</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bukit Nando</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Bukit Nando</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Bukit Nando</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Bukit Nando</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Bukit Nando</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Bukit Nando</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Bukit Nando</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Bukit Nando</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bukit Nando</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Lampion &amp; Dinosaurus Park</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Lampion &amp; Dinosaurus Park</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Lampion &amp; Dinosaurus Park</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Lampion &amp; Dinosaurus Park</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lampion &amp; Dinosaurus Park</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lampion &amp; Dinosaurus Park</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lampion &amp; Dinosaurus Park</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Lampion &amp; Dinosaurus Park</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Lampion &amp; Dinosaurus Park</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Lampion &amp; Dinosaurus Park</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Lampion &amp; Dinosaurus Park</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Lampion &amp; Dinosaurus Park</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lampion &amp; Dinosaurus Park</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Lampion &amp; Dinosaurus Park</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Lampion &amp; Dinosaurus Park</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Batu Rafting</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Hari 1: Harga Wisata (Satuan)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>28500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>28500</v>
+      </c>
+      <c r="D6" t="n">
+        <v>28500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>28500</v>
+      </c>
+      <c r="F6" t="n">
+        <v>28500</v>
+      </c>
+      <c r="G6" t="n">
+        <v>28500</v>
+      </c>
+      <c r="H6" t="n">
+        <v>28500</v>
+      </c>
+      <c r="I6" t="n">
+        <v>28500</v>
+      </c>
+      <c r="J6" t="n">
+        <v>28500</v>
+      </c>
+      <c r="K6" t="n">
+        <v>28500</v>
+      </c>
+      <c r="L6" t="n">
+        <v>28500</v>
+      </c>
+      <c r="M6" t="n">
+        <v>28500</v>
+      </c>
+      <c r="N6" t="n">
+        <v>28500</v>
+      </c>
+      <c r="O6" t="n">
+        <v>28500</v>
+      </c>
+      <c r="P6" t="n">
+        <v>28500</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>90000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>90000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>90000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>90000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>90000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>90000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>90000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>90000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>90000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>90000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>90000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>90000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>90000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>90000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>90000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Hari 1: Makan Pagi</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Depot 200</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Depot 200</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Depot 200</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Depot 200</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Depot 200</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Depot 200</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Depot 200</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Depot 200</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Depot 200</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Depot 200</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Depot 200</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Depot 200</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Depot 200</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Depot 200</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Depot 200</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Depot Shanghai</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Depot Shanghai</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Depot Shanghai</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Depot Shanghai</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Depot Shanghai</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Depot Nank Garasi</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Pondok Desa</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Depot Shanghai</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Depot Shanghai</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Depot Shanghai</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Pondok Desa</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Depot Nank Garasi</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Depot Nank Garasi</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Depot Shanghai</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Pondok Desa</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Veggie Kitchen Malang (Vegetarian Food)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Hari 1: Harga Makan Pagi</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>19000</v>
+      </c>
+      <c r="C8" t="n">
+        <v>19000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>19000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F8" t="n">
+        <v>19000</v>
+      </c>
+      <c r="G8" t="n">
+        <v>19000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>19000</v>
+      </c>
+      <c r="I8" t="n">
+        <v>19000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>19000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>19000</v>
+      </c>
+      <c r="M8" t="n">
+        <v>19000</v>
+      </c>
+      <c r="N8" t="n">
+        <v>19000</v>
+      </c>
+      <c r="O8" t="n">
+        <v>19000</v>
+      </c>
+      <c r="P8" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>34000</v>
+      </c>
+      <c r="R8" t="n">
+        <v>34000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>34000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>34000</v>
+      </c>
+      <c r="U8" t="n">
+        <v>34000</v>
+      </c>
+      <c r="V8" t="n">
+        <v>36018</v>
+      </c>
+      <c r="W8" t="n">
+        <v>35000</v>
+      </c>
+      <c r="X8" t="n">
+        <v>34000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>34000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>34000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>36018</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>36018</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>34000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>55377</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Hari 1: Makan Siang</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Warung Lalapan Mbak Denok</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Warung Lalapan Mbak Denok</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Warung Lalapan Mbak Denok</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Warung Lalapan Mbak Denok</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Warung Lalapan Mbak Denok</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Warung Lalapan Mbak Denok</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Warung Lalapan Mbak Denok</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Warung Lalapan Mbak Denok</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Warung Lalapan Mbak Denok</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Warung Lalapan Mbak Denok</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Warung Lalapan Mbak Denok</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Warung Lalapan Mbak Denok</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Warung Lalapan Mbak Denok</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Warung Lalapan Mbak Denok</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Warung Lalapan Mbak Denok</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Melati Restaurant</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Melati Restaurant</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Melati Restaurant</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Melati Restaurant</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Melati Restaurant</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Melati Restaurant</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Melati Restaurant</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Melati Restaurant</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Melati Restaurant</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Melati Restaurant</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Melati Restaurant</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Melati Restaurant</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Melati Restaurant</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Melati Restaurant</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Melati Restaurant</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>RJB - Rumah Jagal Bapa</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Hari 1: Harga Makan Siang</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>19000</v>
+      </c>
+      <c r="C10" t="n">
+        <v>19000</v>
+      </c>
+      <c r="D10" t="n">
+        <v>19000</v>
+      </c>
+      <c r="E10" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F10" t="n">
+        <v>19000</v>
+      </c>
+      <c r="G10" t="n">
+        <v>19000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>19000</v>
+      </c>
+      <c r="I10" t="n">
+        <v>19000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K10" t="n">
+        <v>19000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>19000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>19000</v>
+      </c>
+      <c r="N10" t="n">
+        <v>19000</v>
+      </c>
+      <c r="O10" t="n">
+        <v>19000</v>
+      </c>
+      <c r="P10" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>36000</v>
+      </c>
+      <c r="R10" t="n">
+        <v>36000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>36000</v>
+      </c>
+      <c r="T10" t="n">
+        <v>36000</v>
+      </c>
+      <c r="U10" t="n">
+        <v>36000</v>
+      </c>
+      <c r="V10" t="n">
+        <v>36000</v>
+      </c>
+      <c r="W10" t="n">
+        <v>36000</v>
+      </c>
+      <c r="X10" t="n">
+        <v>36000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>36000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>36000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>36000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>36000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>36000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>36000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>36000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Hari 1: Makan Malam</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Pondok Desa</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Depot Nank Garasi</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Rawon Nguling</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Pondok Desa</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Pondok Desa</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Depot Nank Garasi</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Warung Sate Gule Bang Tismanto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Hari 1: Harga Makan Malam</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>19000</v>
+      </c>
+      <c r="C12" t="n">
+        <v>19000</v>
+      </c>
+      <c r="D12" t="n">
+        <v>19000</v>
+      </c>
+      <c r="E12" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F12" t="n">
+        <v>19000</v>
+      </c>
+      <c r="G12" t="n">
+        <v>19000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>19000</v>
+      </c>
+      <c r="I12" t="n">
+        <v>19000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K12" t="n">
+        <v>19000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>19000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>19000</v>
+      </c>
+      <c r="N12" t="n">
+        <v>19000</v>
+      </c>
+      <c r="O12" t="n">
+        <v>19000</v>
+      </c>
+      <c r="P12" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>35385</v>
+      </c>
+      <c r="R12" t="n">
+        <v>35385</v>
+      </c>
+      <c r="S12" t="n">
+        <v>35385</v>
+      </c>
+      <c r="T12" t="n">
+        <v>35385</v>
+      </c>
+      <c r="U12" t="n">
+        <v>35385</v>
+      </c>
+      <c r="V12" t="n">
+        <v>35000</v>
+      </c>
+      <c r="W12" t="n">
+        <v>36018</v>
+      </c>
+      <c r="X12" t="n">
+        <v>35385</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>35385</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>35385</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>34400</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>35385</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>36018</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Hari 1: Cost Kamar Hotel (1 Malam x 1 Kamar)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>182484</v>
+      </c>
+      <c r="C13" t="n">
+        <v>182484</v>
+      </c>
+      <c r="D13" t="n">
+        <v>182484</v>
+      </c>
+      <c r="E13" t="n">
+        <v>182484</v>
+      </c>
+      <c r="F13" t="n">
+        <v>182484</v>
+      </c>
+      <c r="G13" t="n">
+        <v>182484</v>
+      </c>
+      <c r="H13" t="n">
+        <v>182484</v>
+      </c>
+      <c r="I13" t="n">
+        <v>182484</v>
+      </c>
+      <c r="J13" t="n">
+        <v>182484</v>
+      </c>
+      <c r="K13" t="n">
+        <v>182484</v>
+      </c>
+      <c r="L13" t="n">
+        <v>182484</v>
+      </c>
+      <c r="M13" t="n">
+        <v>182484</v>
+      </c>
+      <c r="N13" t="n">
+        <v>182484</v>
+      </c>
+      <c r="O13" t="n">
+        <v>182484</v>
+      </c>
+      <c r="P13" t="n">
+        <v>182484</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>327600</v>
+      </c>
+      <c r="R13" t="n">
+        <v>327600</v>
+      </c>
+      <c r="S13" t="n">
+        <v>327600</v>
+      </c>
+      <c r="T13" t="n">
+        <v>327600</v>
+      </c>
+      <c r="U13" t="n">
+        <v>327600</v>
+      </c>
+      <c r="V13" t="n">
+        <v>307162</v>
+      </c>
+      <c r="W13" t="n">
+        <v>313066</v>
+      </c>
+      <c r="X13" t="n">
+        <v>327600</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>327600</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>327600</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>318189</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>307162</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>307162</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>309517</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>313066</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Hari 1: Cost Tiket Wisata (1 Orang)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>28500</v>
+      </c>
+      <c r="C14" t="n">
+        <v>28500</v>
+      </c>
+      <c r="D14" t="n">
+        <v>28500</v>
+      </c>
+      <c r="E14" t="n">
+        <v>28500</v>
+      </c>
+      <c r="F14" t="n">
+        <v>28500</v>
+      </c>
+      <c r="G14" t="n">
+        <v>28500</v>
+      </c>
+      <c r="H14" t="n">
+        <v>28500</v>
+      </c>
+      <c r="I14" t="n">
+        <v>28500</v>
+      </c>
+      <c r="J14" t="n">
+        <v>28500</v>
+      </c>
+      <c r="K14" t="n">
+        <v>28500</v>
+      </c>
+      <c r="L14" t="n">
+        <v>28500</v>
+      </c>
+      <c r="M14" t="n">
+        <v>28500</v>
+      </c>
+      <c r="N14" t="n">
+        <v>28500</v>
+      </c>
+      <c r="O14" t="n">
+        <v>28500</v>
+      </c>
+      <c r="P14" t="n">
+        <v>28500</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>90000</v>
+      </c>
+      <c r="R14" t="n">
+        <v>90000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>90000</v>
+      </c>
+      <c r="T14" t="n">
+        <v>90000</v>
+      </c>
+      <c r="U14" t="n">
+        <v>90000</v>
+      </c>
+      <c r="V14" t="n">
+        <v>90000</v>
+      </c>
+      <c r="W14" t="n">
+        <v>90000</v>
+      </c>
+      <c r="X14" t="n">
+        <v>90000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>90000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>90000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>90000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>90000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>90000</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>90000</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>90000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Hari 1: Cost Kuliner (1 Orang x 3x Makan)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>57000</v>
+      </c>
+      <c r="C15" t="n">
+        <v>57000</v>
+      </c>
+      <c r="D15" t="n">
+        <v>57000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>57000</v>
+      </c>
+      <c r="F15" t="n">
+        <v>57000</v>
+      </c>
+      <c r="G15" t="n">
+        <v>57000</v>
+      </c>
+      <c r="H15" t="n">
+        <v>57000</v>
+      </c>
+      <c r="I15" t="n">
+        <v>57000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>57000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>57000</v>
+      </c>
+      <c r="L15" t="n">
+        <v>57000</v>
+      </c>
+      <c r="M15" t="n">
+        <v>57000</v>
+      </c>
+      <c r="N15" t="n">
+        <v>57000</v>
+      </c>
+      <c r="O15" t="n">
+        <v>57000</v>
+      </c>
+      <c r="P15" t="n">
+        <v>57000</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>105385</v>
+      </c>
+      <c r="R15" t="n">
+        <v>105385</v>
+      </c>
+      <c r="S15" t="n">
+        <v>105385</v>
+      </c>
+      <c r="T15" t="n">
+        <v>105385</v>
+      </c>
+      <c r="U15" t="n">
+        <v>105385</v>
+      </c>
+      <c r="V15" t="n">
+        <v>107018</v>
+      </c>
+      <c r="W15" t="n">
+        <v>107018</v>
+      </c>
+      <c r="X15" t="n">
+        <v>105385</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>105385</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>105385</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>105400</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>107018</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>107018</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>105385</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>107018</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>205377</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Hari 1: Cost Transportasi (Porsi Harian Flat)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>302146</v>
+      </c>
+      <c r="C16" t="n">
+        <v>302146</v>
+      </c>
+      <c r="D16" t="n">
+        <v>302146</v>
+      </c>
+      <c r="E16" t="n">
+        <v>302146</v>
+      </c>
+      <c r="F16" t="n">
+        <v>302146</v>
+      </c>
+      <c r="G16" t="n">
+        <v>302146</v>
+      </c>
+      <c r="H16" t="n">
+        <v>302146</v>
+      </c>
+      <c r="I16" t="n">
+        <v>302146</v>
+      </c>
+      <c r="J16" t="n">
+        <v>302146</v>
+      </c>
+      <c r="K16" t="n">
+        <v>302146</v>
+      </c>
+      <c r="L16" t="n">
+        <v>302146</v>
+      </c>
+      <c r="M16" t="n">
+        <v>302146</v>
+      </c>
+      <c r="N16" t="n">
+        <v>302146</v>
+      </c>
+      <c r="O16" t="n">
+        <v>302146</v>
+      </c>
+      <c r="P16" t="n">
+        <v>302146</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>71996</v>
+      </c>
+      <c r="R16" t="n">
+        <v>71996</v>
+      </c>
+      <c r="S16" t="n">
+        <v>71996</v>
+      </c>
+      <c r="T16" t="n">
+        <v>71996</v>
+      </c>
+      <c r="U16" t="n">
+        <v>71996</v>
+      </c>
+      <c r="V16" t="n">
+        <v>77849</v>
+      </c>
+      <c r="W16" t="n">
+        <v>78134</v>
+      </c>
+      <c r="X16" t="n">
+        <v>71996</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>71996</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>71996</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>79106</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>77849</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>77849</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>80383</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>78134</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>137908</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Hari 1: Jarak Makan Pagi -&gt; Wisata (km)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="C17" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="D17" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="E17" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="F17" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="G17" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="H17" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="I17" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="J17" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="K17" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="L17" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="M17" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="O17" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="P17" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="V17" t="n">
+        <v>10</v>
+      </c>
+      <c r="W17" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>17.73</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Hari 1: Jarak Wisata -&gt; Makan Siang (km)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="C18" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="E18" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="G18" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="I18" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="J18" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="K18" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="L18" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="M18" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="N18" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="O18" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="P18" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="R18" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="S18" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="T18" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="U18" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="W18" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="X18" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>14.03</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Hari 1: Jarak Makan Siang -&gt; Hotel (km)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="D19" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="E19" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="F19" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="G19" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="H19" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="I19" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="J19" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="K19" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="L19" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="M19" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="N19" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="O19" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="P19" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="X19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>18.04</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Hari 1: Jarak Hotel -&gt; Makan Malam (km)</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>12.54</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Hari 1: Jarak Makan Malam -&gt; Hotel (km)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>12.54</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Hari 1: Total Jarak Hari 1 (km)</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="C22" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="G22" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="L22" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="M22" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="N22" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="O22" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="P22" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="R22" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="S22" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="T22" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="U22" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="V22" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="X22" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>22.84</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>74.90000000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Hari 1: Subtotal Hari 1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>570130</v>
+      </c>
+      <c r="C23" t="n">
+        <v>570130</v>
+      </c>
+      <c r="D23" t="n">
+        <v>570130</v>
+      </c>
+      <c r="E23" t="n">
+        <v>570130</v>
+      </c>
+      <c r="F23" t="n">
+        <v>570130</v>
+      </c>
+      <c r="G23" t="n">
+        <v>570130</v>
+      </c>
+      <c r="H23" t="n">
+        <v>570130</v>
+      </c>
+      <c r="I23" t="n">
+        <v>570130</v>
+      </c>
+      <c r="J23" t="n">
+        <v>570130</v>
+      </c>
+      <c r="K23" t="n">
+        <v>570130</v>
+      </c>
+      <c r="L23" t="n">
+        <v>570130</v>
+      </c>
+      <c r="M23" t="n">
+        <v>570130</v>
+      </c>
+      <c r="N23" t="n">
+        <v>570130</v>
+      </c>
+      <c r="O23" t="n">
+        <v>570130</v>
+      </c>
+      <c r="P23" t="n">
+        <v>570130</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>594981</v>
+      </c>
+      <c r="R23" t="n">
+        <v>594981</v>
+      </c>
+      <c r="S23" t="n">
+        <v>594981</v>
+      </c>
+      <c r="T23" t="n">
+        <v>594981</v>
+      </c>
+      <c r="U23" t="n">
+        <v>594981</v>
+      </c>
+      <c r="V23" t="n">
+        <v>582029</v>
+      </c>
+      <c r="W23" t="n">
+        <v>588218</v>
+      </c>
+      <c r="X23" t="n">
+        <v>594981</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>594981</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>594981</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>592695</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>582029</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>582029</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>585285</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>588218</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1343285</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Hari 2: Hotel</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Hari 2: Harga Hotel (Satuan)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Hari 2: Wisata</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TRANS Wisata Belah Duren</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TRANS Wisata Belah Duren</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TRANS Wisata Belah Duren</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>TRANS Wisata Belah Duren</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>TRANS Wisata Belah Duren</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>TRANS Wisata Belah Duren</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>TRANS Wisata Belah Duren</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>TRANS Wisata Belah Duren</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>TRANS Wisata Belah Duren</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>TRANS Wisata Belah Duren</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>TRANS Wisata Belah Duren</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>TRANS Wisata Belah Duren</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>TRANS Wisata Belah Duren</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>TRANS Wisata Belah Duren</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>TRANS Wisata Belah Duren</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Milenial Glow Garden</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Milenial Glow Garden</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Milenial Glow Garden</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Milenial Glow Garden</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Milenial Glow Garden</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Milenial Glow Garden</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Milenial Glow Garden</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Milenial Glow Garden</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Milenial Glow Garden</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Milenial Glow Garden</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Milenial Glow Garden</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Milenial Glow Garden</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Milenial Glow Garden</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>Milenial Glow Garden</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Milenial Glow Garden</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Meeting Point Pujon Rafting</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Hari 2: Harga Wisata (Satuan)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C27" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D27" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E27" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F27" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G27" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I27" t="n">
+        <v>25000</v>
+      </c>
+      <c r="J27" t="n">
+        <v>25000</v>
+      </c>
+      <c r="K27" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L27" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M27" t="n">
+        <v>25000</v>
+      </c>
+      <c r="N27" t="n">
+        <v>25000</v>
+      </c>
+      <c r="O27" t="n">
+        <v>25000</v>
+      </c>
+      <c r="P27" t="n">
+        <v>25000</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>89100</v>
+      </c>
+      <c r="R27" t="n">
+        <v>89100</v>
+      </c>
+      <c r="S27" t="n">
+        <v>89100</v>
+      </c>
+      <c r="T27" t="n">
+        <v>89100</v>
+      </c>
+      <c r="U27" t="n">
+        <v>89100</v>
+      </c>
+      <c r="V27" t="n">
+        <v>89100</v>
+      </c>
+      <c r="W27" t="n">
+        <v>89100</v>
+      </c>
+      <c r="X27" t="n">
+        <v>89100</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>89100</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>89100</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>89100</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>89100</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>89100</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>89100</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>89100</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>195000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Hari 2: Makan Pagi</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kedai Kopi Mbok gandul tujinem</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pondok Desa</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Depot Nank Garasi</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Rawon Nguling</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Pondok Desa</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Pondok Desa</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Depot 2 Legenda</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>Depot Nank Garasi</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>Warung Sate Gule Bang Tismanto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Hari 2: Harga Makan Pagi</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>19000</v>
+      </c>
+      <c r="C29" t="n">
+        <v>19000</v>
+      </c>
+      <c r="D29" t="n">
+        <v>19000</v>
+      </c>
+      <c r="E29" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F29" t="n">
+        <v>19000</v>
+      </c>
+      <c r="G29" t="n">
+        <v>19000</v>
+      </c>
+      <c r="H29" t="n">
+        <v>19000</v>
+      </c>
+      <c r="I29" t="n">
+        <v>19000</v>
+      </c>
+      <c r="J29" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K29" t="n">
+        <v>19000</v>
+      </c>
+      <c r="L29" t="n">
+        <v>19000</v>
+      </c>
+      <c r="M29" t="n">
+        <v>19000</v>
+      </c>
+      <c r="N29" t="n">
+        <v>19000</v>
+      </c>
+      <c r="O29" t="n">
+        <v>19000</v>
+      </c>
+      <c r="P29" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>35385</v>
+      </c>
+      <c r="R29" t="n">
+        <v>35385</v>
+      </c>
+      <c r="S29" t="n">
+        <v>35385</v>
+      </c>
+      <c r="T29" t="n">
+        <v>35385</v>
+      </c>
+      <c r="U29" t="n">
+        <v>35385</v>
+      </c>
+      <c r="V29" t="n">
+        <v>35000</v>
+      </c>
+      <c r="W29" t="n">
+        <v>36018</v>
+      </c>
+      <c r="X29" t="n">
+        <v>35385</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>35385</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>35385</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>34400</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>35385</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>36018</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Hari 2: Makan Siang</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Rumah Makan Padang SEDERHANA BARU</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Rumah Makan Padang SEDERHANA BARU</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Rumah Makan Padang SEDERHANA BARU</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Rumah Makan Padang SEDERHANA BARU</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rumah Makan Padang SEDERHANA BARU</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Rumah Makan Padang SEDERHANA BARU</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Rumah Makan Padang SEDERHANA BARU</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Rumah Makan Padang SEDERHANA BARU</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Rumah Makan Padang SEDERHANA BARU</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Rumah Makan Padang SEDERHANA BARU</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Rumah Makan Padang SEDERHANA BARU</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Rumah Makan Padang SEDERHANA BARU</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Rumah Makan Padang SEDERHANA BARU</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Rumah Makan Padang SEDERHANA BARU</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Rumah Makan Padang SEDERHANA BARU</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Pondok Gurame Nagarema</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Pondok Gurame Nagarema</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Pondok Gurame Nagarema</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Pondok Gurame Nagarema</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Pondok Gurame Nagarema</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Pondok Gurame Nagarema</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Pondok Gurame Nagarema</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Pondok Gurame Nagarema</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Pondok Gurame Nagarema</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Pondok Gurame Nagarema</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Pondok Gurame Nagarema</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Pondok Gurame Nagarema</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Pondok Gurame Nagarema</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Pondok Gurame Nagarema</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>Pondok Gurame Nagarema</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>Sop Janda Suroboyo - BATU MALANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Hari 2: Harga Makan Siang</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>19000</v>
+      </c>
+      <c r="C31" t="n">
+        <v>19000</v>
+      </c>
+      <c r="D31" t="n">
+        <v>19000</v>
+      </c>
+      <c r="E31" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F31" t="n">
+        <v>19000</v>
+      </c>
+      <c r="G31" t="n">
+        <v>19000</v>
+      </c>
+      <c r="H31" t="n">
+        <v>19000</v>
+      </c>
+      <c r="I31" t="n">
+        <v>19000</v>
+      </c>
+      <c r="J31" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K31" t="n">
+        <v>19000</v>
+      </c>
+      <c r="L31" t="n">
+        <v>19000</v>
+      </c>
+      <c r="M31" t="n">
+        <v>19000</v>
+      </c>
+      <c r="N31" t="n">
+        <v>19000</v>
+      </c>
+      <c r="O31" t="n">
+        <v>19000</v>
+      </c>
+      <c r="P31" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>36000</v>
+      </c>
+      <c r="R31" t="n">
+        <v>36000</v>
+      </c>
+      <c r="S31" t="n">
+        <v>36000</v>
+      </c>
+      <c r="T31" t="n">
+        <v>36000</v>
+      </c>
+      <c r="U31" t="n">
+        <v>36000</v>
+      </c>
+      <c r="V31" t="n">
+        <v>36000</v>
+      </c>
+      <c r="W31" t="n">
+        <v>36000</v>
+      </c>
+      <c r="X31" t="n">
+        <v>36000</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>36000</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>36000</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>36000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>36000</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>36000</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>36000</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>36000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>68500</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Hari 2: Makan Malam</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
-      </c>
-      <c r="N32" t="n">
-        <v>16258</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1467258</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>32742</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>UNDER BUDGET</t>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>Hari 2: Harga Makan Malam</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Sea Villa Kota Batu</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>BatuPaintball</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>130000</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>130000</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>De Bamboo Restaurant</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>51182</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>307092</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>38695</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>1475787</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>24213</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>Hari 2: Cost Kamar Hotel (0 Malam)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>813000</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>813000</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>BatuPaintball</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>130000</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>130000</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Sop Janda Suroboyo - BATU MALANG</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>68500</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>411000</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>22.18</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>49900</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>1403900</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>96100</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>Hari 2: Cost Tiket Wisata (1 Orang)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
-        </is>
+        <v>25000</v>
+      </c>
+      <c r="C35" t="n">
+        <v>25000</v>
       </c>
       <c r="D35" t="n">
-        <v>813000</v>
+        <v>25000</v>
       </c>
       <c r="E35" t="n">
-        <v>813000</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>BatuPaintball</t>
-        </is>
+        <v>25000</v>
+      </c>
+      <c r="F35" t="n">
+        <v>25000</v>
       </c>
       <c r="G35" t="n">
-        <v>130000</v>
+        <v>25000</v>
       </c>
       <c r="H35" t="n">
-        <v>130000</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>De Bamboo Restaurant</t>
-        </is>
+        <v>25000</v>
+      </c>
+      <c r="I35" t="n">
+        <v>25000</v>
       </c>
       <c r="J35" t="n">
-        <v>51182</v>
+        <v>25000</v>
       </c>
       <c r="K35" t="n">
-        <v>307092</v>
+        <v>25000</v>
       </c>
       <c r="L35" t="n">
-        <v>22.33</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
+        <v>25000</v>
+      </c>
+      <c r="M35" t="n">
+        <v>25000</v>
       </c>
       <c r="N35" t="n">
-        <v>50238</v>
+        <v>25000</v>
       </c>
       <c r="O35" t="n">
-        <v>1300330</v>
+        <v>25000</v>
       </c>
       <c r="P35" t="n">
-        <v>1500000</v>
+        <v>25000</v>
       </c>
       <c r="Q35" t="n">
-        <v>199670</v>
+        <v>89100</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
+        <v>89100</v>
+      </c>
+      <c r="S35" t="n">
+        <v>89100</v>
+      </c>
+      <c r="T35" t="n">
+        <v>89100</v>
+      </c>
+      <c r="U35" t="n">
+        <v>89100</v>
+      </c>
+      <c r="V35" t="n">
+        <v>89100</v>
+      </c>
+      <c r="W35" t="n">
+        <v>89100</v>
+      </c>
+      <c r="X35" t="n">
+        <v>89100</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>89100</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>89100</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>89100</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>89100</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>89100</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>89100</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>89100</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>195000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>Hari 2: Cost Kuliner (1 Orang x 2x Makan)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
-        </is>
+        <v>38000</v>
+      </c>
+      <c r="C36" t="n">
+        <v>38000</v>
       </c>
       <c r="D36" t="n">
-        <v>813000</v>
+        <v>38000</v>
       </c>
       <c r="E36" t="n">
-        <v>813000</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>BatuPaintball</t>
-        </is>
+        <v>38000</v>
+      </c>
+      <c r="F36" t="n">
+        <v>38000</v>
       </c>
       <c r="G36" t="n">
-        <v>130000</v>
+        <v>38000</v>
       </c>
       <c r="H36" t="n">
-        <v>130000</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Kutaraja Boutique Restaurant</t>
-        </is>
+        <v>38000</v>
+      </c>
+      <c r="I36" t="n">
+        <v>38000</v>
       </c>
       <c r="J36" t="n">
-        <v>53500</v>
+        <v>38000</v>
       </c>
       <c r="K36" t="n">
-        <v>321000</v>
+        <v>38000</v>
       </c>
       <c r="L36" t="n">
-        <v>22.46</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
+        <v>38000</v>
+      </c>
+      <c r="M36" t="n">
+        <v>38000</v>
       </c>
       <c r="N36" t="n">
-        <v>50527</v>
+        <v>38000</v>
       </c>
       <c r="O36" t="n">
-        <v>1314527</v>
+        <v>38000</v>
       </c>
       <c r="P36" t="n">
-        <v>1500000</v>
+        <v>38000</v>
       </c>
       <c r="Q36" t="n">
-        <v>185473</v>
+        <v>71385</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
+        <v>71385</v>
+      </c>
+      <c r="S36" t="n">
+        <v>71385</v>
+      </c>
+      <c r="T36" t="n">
+        <v>71385</v>
+      </c>
+      <c r="U36" t="n">
+        <v>71385</v>
+      </c>
+      <c r="V36" t="n">
+        <v>71000</v>
+      </c>
+      <c r="W36" t="n">
+        <v>72018</v>
+      </c>
+      <c r="X36" t="n">
+        <v>71385</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>71385</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>71385</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>70400</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>71000</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>71000</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>71385</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>72018</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>128500</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>Hari 2: Cost Transportasi (Porsi Harian Flat)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
-        </is>
+        <v>302145</v>
+      </c>
+      <c r="C37" t="n">
+        <v>302145</v>
       </c>
       <c r="D37" t="n">
-        <v>813000</v>
+        <v>302145</v>
       </c>
       <c r="E37" t="n">
-        <v>813000</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>BatuPaintball</t>
-        </is>
+        <v>302145</v>
+      </c>
+      <c r="F37" t="n">
+        <v>302145</v>
       </c>
       <c r="G37" t="n">
-        <v>130000</v>
+        <v>302145</v>
       </c>
       <c r="H37" t="n">
-        <v>130000</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Warung Sate Gule Bang Tismanto</t>
-        </is>
+        <v>302145</v>
+      </c>
+      <c r="I37" t="n">
+        <v>302145</v>
       </c>
       <c r="J37" t="n">
-        <v>60000</v>
+        <v>302145</v>
       </c>
       <c r="K37" t="n">
-        <v>360000</v>
+        <v>302145</v>
       </c>
       <c r="L37" t="n">
-        <v>38.01</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
+        <v>302145</v>
+      </c>
+      <c r="M37" t="n">
+        <v>302145</v>
       </c>
       <c r="N37" t="n">
-        <v>85530</v>
+        <v>302145</v>
       </c>
       <c r="O37" t="n">
-        <v>1388530</v>
+        <v>302145</v>
       </c>
       <c r="P37" t="n">
-        <v>1500000</v>
+        <v>302145</v>
       </c>
       <c r="Q37" t="n">
-        <v>111470</v>
+        <v>71996</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
+        <v>71996</v>
+      </c>
+      <c r="S37" t="n">
+        <v>71996</v>
+      </c>
+      <c r="T37" t="n">
+        <v>71996</v>
+      </c>
+      <c r="U37" t="n">
+        <v>71996</v>
+      </c>
+      <c r="V37" t="n">
+        <v>77849</v>
+      </c>
+      <c r="W37" t="n">
+        <v>78134</v>
+      </c>
+      <c r="X37" t="n">
+        <v>71996</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>71996</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>71996</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>79106</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>77849</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>77849</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>80383</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>78134</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>137909</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>Hari 2: Jarak Hotel -&gt; Makan Pagi (km)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
-        </is>
+        <v>1.3</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1.3</v>
       </c>
       <c r="D38" t="n">
-        <v>813000</v>
+        <v>1.3</v>
       </c>
       <c r="E38" t="n">
-        <v>813000</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>BatuPaintball</t>
-        </is>
+        <v>1.3</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.3</v>
       </c>
       <c r="G38" t="n">
-        <v>130000</v>
+        <v>1.3</v>
       </c>
       <c r="H38" t="n">
-        <v>130000</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>DAPUR LAWAS MALANG</t>
-        </is>
+        <v>1.3</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
-        <v>58500</v>
+        <v>1.3</v>
       </c>
       <c r="K38" t="n">
-        <v>351000</v>
+        <v>1.3</v>
       </c>
       <c r="L38" t="n">
-        <v>46.29</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
+        <v>1.3</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.3</v>
       </c>
       <c r="N38" t="n">
-        <v>104153</v>
+        <v>1.3</v>
       </c>
       <c r="O38" t="n">
-        <v>1398153</v>
+        <v>1.3</v>
       </c>
       <c r="P38" t="n">
-        <v>1500000</v>
+        <v>1.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>101847</v>
+        <v>0.31</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
+        <v>0.31</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>12.54</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>Hari 2: Jarak Makan Pagi -&gt; Wisata (km)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>8</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="C39" t="n">
+        <v>30</v>
       </c>
       <c r="D39" t="n">
-        <v>813000</v>
+        <v>30</v>
       </c>
       <c r="E39" t="n">
-        <v>813000</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>BatuPaintball</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="F39" t="n">
+        <v>30</v>
       </c>
       <c r="G39" t="n">
-        <v>130000</v>
+        <v>30</v>
       </c>
       <c r="H39" t="n">
-        <v>130000</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Depot Kanton</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="I39" t="n">
+        <v>30</v>
       </c>
       <c r="J39" t="n">
-        <v>65000</v>
+        <v>30</v>
       </c>
       <c r="K39" t="n">
-        <v>390000</v>
+        <v>30</v>
       </c>
       <c r="L39" t="n">
-        <v>50.29</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="M39" t="n">
+        <v>30</v>
       </c>
       <c r="N39" t="n">
-        <v>113144</v>
+        <v>30</v>
       </c>
       <c r="O39" t="n">
-        <v>1446144</v>
+        <v>30</v>
       </c>
       <c r="P39" t="n">
-        <v>1500000</v>
+        <v>30</v>
       </c>
       <c r="Q39" t="n">
-        <v>53856</v>
+        <v>13.02</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
+        <v>13.02</v>
+      </c>
+      <c r="S39" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="T39" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="U39" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="V39" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="W39" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="X39" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>23.01</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>Hari 2: Jarak Wisata -&gt; Makan Siang (km)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>9</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
-        </is>
+        <v>57.67</v>
+      </c>
+      <c r="C40" t="n">
+        <v>57.67</v>
       </c>
       <c r="D40" t="n">
-        <v>813000</v>
+        <v>57.67</v>
       </c>
       <c r="E40" t="n">
-        <v>813000</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>BatuPaintball</t>
-        </is>
+        <v>57.67</v>
+      </c>
+      <c r="F40" t="n">
+        <v>57.67</v>
       </c>
       <c r="G40" t="n">
-        <v>130000</v>
+        <v>57.67</v>
       </c>
       <c r="H40" t="n">
-        <v>130000</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Depot Widari</t>
-        </is>
+        <v>57.67</v>
+      </c>
+      <c r="I40" t="n">
+        <v>57.67</v>
       </c>
       <c r="J40" t="n">
-        <v>50600</v>
+        <v>57.67</v>
       </c>
       <c r="K40" t="n">
-        <v>303600</v>
+        <v>57.67</v>
       </c>
       <c r="L40" t="n">
-        <v>50.36</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
+        <v>57.67</v>
+      </c>
+      <c r="M40" t="n">
+        <v>57.67</v>
       </c>
       <c r="N40" t="n">
-        <v>113311</v>
+        <v>57.67</v>
       </c>
       <c r="O40" t="n">
-        <v>1359911</v>
+        <v>57.67</v>
       </c>
       <c r="P40" t="n">
-        <v>1500000</v>
+        <v>57.67</v>
       </c>
       <c r="Q40" t="n">
-        <v>140089</v>
+        <v>32.55</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
+        <v>32.55</v>
+      </c>
+      <c r="S40" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="T40" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="U40" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="V40" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="W40" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="X40" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>12.13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>Hari 2: Total Jarak Hari 2 (km)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
-        </is>
+        <v>88.97</v>
+      </c>
+      <c r="C41" t="n">
+        <v>88.97</v>
       </c>
       <c r="D41" t="n">
-        <v>813000</v>
+        <v>88.97</v>
       </c>
       <c r="E41" t="n">
-        <v>813000</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>BatuPaintball</t>
-        </is>
+        <v>88.97</v>
+      </c>
+      <c r="F41" t="n">
+        <v>88.97</v>
       </c>
       <c r="G41" t="n">
-        <v>130000</v>
+        <v>88.97</v>
       </c>
       <c r="H41" t="n">
-        <v>130000</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Depot Santai</t>
-        </is>
+        <v>88.97</v>
+      </c>
+      <c r="I41" t="n">
+        <v>88.97</v>
       </c>
       <c r="J41" t="n">
-        <v>50000</v>
+        <v>88.97</v>
       </c>
       <c r="K41" t="n">
-        <v>300000</v>
+        <v>88.97</v>
       </c>
       <c r="L41" t="n">
-        <v>50.54</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
+        <v>88.97</v>
+      </c>
+      <c r="M41" t="n">
+        <v>88.97</v>
       </c>
       <c r="N41" t="n">
-        <v>113710</v>
+        <v>88.97</v>
       </c>
       <c r="O41" t="n">
-        <v>1356710</v>
+        <v>88.97</v>
       </c>
       <c r="P41" t="n">
-        <v>1500000</v>
+        <v>88.97</v>
       </c>
       <c r="Q41" t="n">
-        <v>143290</v>
+        <v>45.87</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
+        <v>45.87</v>
+      </c>
+      <c r="S41" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="T41" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="U41" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="V41" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="W41" t="n">
+        <v>47.79</v>
+      </c>
+      <c r="X41" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>49.98</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>48.61</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>47.79</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>47.69</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>Hari 2: Subtotal Hari 2</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>11</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
-        </is>
+        <v>365145</v>
+      </c>
+      <c r="C42" t="n">
+        <v>365145</v>
       </c>
       <c r="D42" t="n">
-        <v>813000</v>
+        <v>365145</v>
       </c>
       <c r="E42" t="n">
-        <v>813000</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>BatuPaintball</t>
-        </is>
+        <v>365145</v>
+      </c>
+      <c r="F42" t="n">
+        <v>365145</v>
       </c>
       <c r="G42" t="n">
-        <v>130000</v>
+        <v>365145</v>
       </c>
       <c r="H42" t="n">
-        <v>130000</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Depot Gang Djangkrik</t>
-        </is>
+        <v>365145</v>
+      </c>
+      <c r="I42" t="n">
+        <v>365145</v>
       </c>
       <c r="J42" t="n">
-        <v>65714</v>
+        <v>365145</v>
       </c>
       <c r="K42" t="n">
-        <v>394284</v>
+        <v>365145</v>
       </c>
       <c r="L42" t="n">
-        <v>50.84</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
+        <v>365145</v>
+      </c>
+      <c r="M42" t="n">
+        <v>365145</v>
       </c>
       <c r="N42" t="n">
-        <v>114401</v>
+        <v>365145</v>
       </c>
       <c r="O42" t="n">
-        <v>1451685</v>
+        <v>365145</v>
       </c>
       <c r="P42" t="n">
-        <v>1500000</v>
+        <v>365145</v>
       </c>
       <c r="Q42" t="n">
-        <v>48315</v>
+        <v>232481</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
+        <v>232481</v>
+      </c>
+      <c r="S42" t="n">
+        <v>232481</v>
+      </c>
+      <c r="T42" t="n">
+        <v>232481</v>
+      </c>
+      <c r="U42" t="n">
+        <v>232481</v>
+      </c>
+      <c r="V42" t="n">
+        <v>237949</v>
+      </c>
+      <c r="W42" t="n">
+        <v>239252</v>
+      </c>
+      <c r="X42" t="n">
+        <v>232481</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>232481</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>232481</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>238606</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>237949</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>237949</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>240868</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>239252</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>461409</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>🏨 Akomodasi (1 malam x 1 kamar)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>12</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
-        </is>
+        <v>182484</v>
+      </c>
+      <c r="C43" t="n">
+        <v>182484</v>
       </c>
       <c r="D43" t="n">
-        <v>813000</v>
+        <v>182484</v>
       </c>
       <c r="E43" t="n">
-        <v>813000</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>BatuPaintball</t>
-        </is>
+        <v>182484</v>
+      </c>
+      <c r="F43" t="n">
+        <v>182484</v>
       </c>
       <c r="G43" t="n">
-        <v>130000</v>
+        <v>182484</v>
       </c>
       <c r="H43" t="n">
-        <v>130000</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
-        </is>
+        <v>182484</v>
+      </c>
+      <c r="I43" t="n">
+        <v>182484</v>
       </c>
       <c r="J43" t="n">
-        <v>55500</v>
+        <v>182484</v>
       </c>
       <c r="K43" t="n">
-        <v>333000</v>
+        <v>182484</v>
       </c>
       <c r="L43" t="n">
-        <v>51.02</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
+        <v>182484</v>
+      </c>
+      <c r="M43" t="n">
+        <v>182484</v>
       </c>
       <c r="N43" t="n">
-        <v>114785</v>
+        <v>182484</v>
       </c>
       <c r="O43" t="n">
-        <v>1390785</v>
+        <v>182484</v>
       </c>
       <c r="P43" t="n">
-        <v>1500000</v>
+        <v>182484</v>
       </c>
       <c r="Q43" t="n">
-        <v>109215</v>
+        <v>327600</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
+        <v>327600</v>
+      </c>
+      <c r="S43" t="n">
+        <v>327600</v>
+      </c>
+      <c r="T43" t="n">
+        <v>327600</v>
+      </c>
+      <c r="U43" t="n">
+        <v>327600</v>
+      </c>
+      <c r="V43" t="n">
+        <v>307162</v>
+      </c>
+      <c r="W43" t="n">
+        <v>313066</v>
+      </c>
+      <c r="X43" t="n">
+        <v>327600</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>327600</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>327600</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>318189</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>307162</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>307162</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>309517</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>313066</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>800000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>🎯 Tiket Wisata (1 orang)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>13</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
-        </is>
+        <v>53500</v>
+      </c>
+      <c r="C44" t="n">
+        <v>53500</v>
       </c>
       <c r="D44" t="n">
-        <v>813000</v>
+        <v>53500</v>
       </c>
       <c r="E44" t="n">
-        <v>813000</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>BatuPaintball</t>
-        </is>
+        <v>53500</v>
+      </c>
+      <c r="F44" t="n">
+        <v>53500</v>
       </c>
       <c r="G44" t="n">
-        <v>130000</v>
+        <v>53500</v>
       </c>
       <c r="H44" t="n">
-        <v>130000</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Veggie Kitchen Malang (Vegetarian Food)</t>
-        </is>
+        <v>53500</v>
+      </c>
+      <c r="I44" t="n">
+        <v>53500</v>
       </c>
       <c r="J44" t="n">
-        <v>55377</v>
+        <v>53500</v>
       </c>
       <c r="K44" t="n">
-        <v>332262</v>
+        <v>53500</v>
       </c>
       <c r="L44" t="n">
-        <v>51.31</v>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
+        <v>53500</v>
+      </c>
+      <c r="M44" t="n">
+        <v>53500</v>
       </c>
       <c r="N44" t="n">
-        <v>115445</v>
+        <v>53500</v>
       </c>
       <c r="O44" t="n">
-        <v>1390707</v>
+        <v>53500</v>
       </c>
       <c r="P44" t="n">
-        <v>1500000</v>
+        <v>53500</v>
       </c>
       <c r="Q44" t="n">
-        <v>109293</v>
+        <v>179100</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
+        <v>179100</v>
+      </c>
+      <c r="S44" t="n">
+        <v>179100</v>
+      </c>
+      <c r="T44" t="n">
+        <v>179100</v>
+      </c>
+      <c r="U44" t="n">
+        <v>179100</v>
+      </c>
+      <c r="V44" t="n">
+        <v>179100</v>
+      </c>
+      <c r="W44" t="n">
+        <v>179100</v>
+      </c>
+      <c r="X44" t="n">
+        <v>179100</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>179100</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>179100</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>179100</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>179100</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>179100</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>179100</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>179100</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>395000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>🍜 Kuliner (1 orang x 5 total makan)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>14</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Bobocabin Coban Rondo, Malang</t>
-        </is>
+        <v>95000</v>
+      </c>
+      <c r="C45" t="n">
+        <v>95000</v>
       </c>
       <c r="D45" t="n">
-        <v>813000</v>
+        <v>95000</v>
       </c>
       <c r="E45" t="n">
-        <v>813000</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>BatuPaintball</t>
-        </is>
+        <v>95000</v>
+      </c>
+      <c r="F45" t="n">
+        <v>95000</v>
       </c>
       <c r="G45" t="n">
-        <v>130000</v>
+        <v>95000</v>
       </c>
       <c r="H45" t="n">
-        <v>130000</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Depot 88 - Araya</t>
-        </is>
+        <v>95000</v>
+      </c>
+      <c r="I45" t="n">
+        <v>95000</v>
       </c>
       <c r="J45" t="n">
-        <v>58750</v>
+        <v>95000</v>
       </c>
       <c r="K45" t="n">
-        <v>352500</v>
+        <v>95000</v>
       </c>
       <c r="L45" t="n">
-        <v>54.02</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
+        <v>95000</v>
+      </c>
+      <c r="M45" t="n">
+        <v>95000</v>
       </c>
       <c r="N45" t="n">
-        <v>121547</v>
+        <v>95000</v>
       </c>
       <c r="O45" t="n">
-        <v>1417047</v>
+        <v>95000</v>
       </c>
       <c r="P45" t="n">
-        <v>1500000</v>
+        <v>95000</v>
       </c>
       <c r="Q45" t="n">
-        <v>82953</v>
+        <v>176770</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
+        <v>176770</v>
+      </c>
+      <c r="S45" t="n">
+        <v>176770</v>
+      </c>
+      <c r="T45" t="n">
+        <v>176770</v>
+      </c>
+      <c r="U45" t="n">
+        <v>176770</v>
+      </c>
+      <c r="V45" t="n">
+        <v>178018</v>
+      </c>
+      <c r="W45" t="n">
+        <v>179036</v>
+      </c>
+      <c r="X45" t="n">
+        <v>176770</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>176770</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>176770</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>175800</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>178018</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>178018</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>176770</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>179036</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>333877</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>🚗 Transportasi (Motor GoRide (1 orang))</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>15</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Hotel Kawi Surapatha</t>
-        </is>
+        <v>604291</v>
+      </c>
+      <c r="C46" t="n">
+        <v>604291</v>
       </c>
       <c r="D46" t="n">
-        <v>800000</v>
+        <v>604291</v>
       </c>
       <c r="E46" t="n">
-        <v>800000</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>BatuPaintball</t>
-        </is>
+        <v>604291</v>
+      </c>
+      <c r="F46" t="n">
+        <v>604291</v>
       </c>
       <c r="G46" t="n">
-        <v>130000</v>
+        <v>604291</v>
       </c>
       <c r="H46" t="n">
-        <v>130000</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Kutaraja Boutique Restaurant</t>
-        </is>
+        <v>604291</v>
+      </c>
+      <c r="I46" t="n">
+        <v>604291</v>
       </c>
       <c r="J46" t="n">
-        <v>53500</v>
+        <v>604291</v>
       </c>
       <c r="K46" t="n">
-        <v>321000</v>
+        <v>604291</v>
       </c>
       <c r="L46" t="n">
-        <v>44.83</v>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Motor GoRide (1 orang)</t>
-        </is>
+        <v>604291</v>
+      </c>
+      <c r="M46" t="n">
+        <v>604291</v>
       </c>
       <c r="N46" t="n">
-        <v>100875</v>
+        <v>604291</v>
       </c>
       <c r="O46" t="n">
-        <v>1351875</v>
+        <v>604291</v>
       </c>
       <c r="P46" t="n">
-        <v>1500000</v>
+        <v>604291</v>
       </c>
       <c r="Q46" t="n">
-        <v>148125</v>
+        <v>143992</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>UNDER BUDGET</t>
-        </is>
+        <v>143992</v>
+      </c>
+      <c r="S46" t="n">
+        <v>143992</v>
+      </c>
+      <c r="T46" t="n">
+        <v>143992</v>
+      </c>
+      <c r="U46" t="n">
+        <v>143992</v>
+      </c>
+      <c r="V46" t="n">
+        <v>155698</v>
+      </c>
+      <c r="W46" t="n">
+        <v>156268</v>
+      </c>
+      <c r="X46" t="n">
+        <v>143992</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>143992</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>143992</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>158212</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>155698</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>155698</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>160766</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>156268</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>275817</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>💰 ESTIMASI TOTAL BIAYA PAKET</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>935275</v>
+      </c>
+      <c r="C47" t="n">
+        <v>935275</v>
+      </c>
+      <c r="D47" t="n">
+        <v>935275</v>
+      </c>
+      <c r="E47" t="n">
+        <v>935275</v>
+      </c>
+      <c r="F47" t="n">
+        <v>935275</v>
+      </c>
+      <c r="G47" t="n">
+        <v>935275</v>
+      </c>
+      <c r="H47" t="n">
+        <v>935275</v>
+      </c>
+      <c r="I47" t="n">
+        <v>935275</v>
+      </c>
+      <c r="J47" t="n">
+        <v>935275</v>
+      </c>
+      <c r="K47" t="n">
+        <v>935275</v>
+      </c>
+      <c r="L47" t="n">
+        <v>935275</v>
+      </c>
+      <c r="M47" t="n">
+        <v>935275</v>
+      </c>
+      <c r="N47" t="n">
+        <v>935275</v>
+      </c>
+      <c r="O47" t="n">
+        <v>935275</v>
+      </c>
+      <c r="P47" t="n">
+        <v>935275</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>827462</v>
+      </c>
+      <c r="R47" t="n">
+        <v>827462</v>
+      </c>
+      <c r="S47" t="n">
+        <v>827462</v>
+      </c>
+      <c r="T47" t="n">
+        <v>827462</v>
+      </c>
+      <c r="U47" t="n">
+        <v>827462</v>
+      </c>
+      <c r="V47" t="n">
+        <v>819978</v>
+      </c>
+      <c r="W47" t="n">
+        <v>827470</v>
+      </c>
+      <c r="X47" t="n">
+        <v>827462</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>827462</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>827462</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>831301</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>819978</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>819978</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>826153</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>827470</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1804694</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total Jarak Spasial Seluruh Hari (km)</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="C48" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="D48" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="E48" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="F48" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="G48" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="H48" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="I48" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="J48" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="K48" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="L48" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="M48" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="N48" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="O48" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="P48" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>64</v>
+      </c>
+      <c r="R48" t="n">
+        <v>64</v>
+      </c>
+      <c r="S48" t="n">
+        <v>64</v>
+      </c>
+      <c r="T48" t="n">
+        <v>64</v>
+      </c>
+      <c r="U48" t="n">
+        <v>64</v>
+      </c>
+      <c r="V48" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="W48" t="n">
+        <v>69.45</v>
+      </c>
+      <c r="X48" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>64</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>70.31999999999999</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>71.45</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>69.45</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>122.59</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>💵 Sisa Anggaran (Kembalian)</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>564725</v>
+      </c>
+      <c r="C49" t="n">
+        <v>564725</v>
+      </c>
+      <c r="D49" t="n">
+        <v>564725</v>
+      </c>
+      <c r="E49" t="n">
+        <v>564725</v>
+      </c>
+      <c r="F49" t="n">
+        <v>564725</v>
+      </c>
+      <c r="G49" t="n">
+        <v>564725</v>
+      </c>
+      <c r="H49" t="n">
+        <v>564725</v>
+      </c>
+      <c r="I49" t="n">
+        <v>564725</v>
+      </c>
+      <c r="J49" t="n">
+        <v>564725</v>
+      </c>
+      <c r="K49" t="n">
+        <v>564725</v>
+      </c>
+      <c r="L49" t="n">
+        <v>564725</v>
+      </c>
+      <c r="M49" t="n">
+        <v>564725</v>
+      </c>
+      <c r="N49" t="n">
+        <v>564725</v>
+      </c>
+      <c r="O49" t="n">
+        <v>564725</v>
+      </c>
+      <c r="P49" t="n">
+        <v>564725</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>672538</v>
+      </c>
+      <c r="R49" t="n">
+        <v>672538</v>
+      </c>
+      <c r="S49" t="n">
+        <v>672538</v>
+      </c>
+      <c r="T49" t="n">
+        <v>672538</v>
+      </c>
+      <c r="U49" t="n">
+        <v>672538</v>
+      </c>
+      <c r="V49" t="n">
+        <v>680022</v>
+      </c>
+      <c r="W49" t="n">
+        <v>672530</v>
+      </c>
+      <c r="X49" t="n">
+        <v>672538</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>672538</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>672538</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>668699</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>680022</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>680022</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>673847</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>672530</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>💸 Kelebihan Anggaran (Nominal)</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>304694</v>
       </c>
     </row>
   </sheetData>

--- a/SIMULATION/EXPERIMENT MODEL/START/rekomendasi_paket.xlsx
+++ b/SIMULATION/EXPERIMENT MODEL/START/rekomendasi_paket.xlsx
@@ -3224,18 +3224,18 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kos Putra Bulanan</t>
+          <t>THE 1O1 Malang OJ</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>600000</v>
+        <v>591601</v>
       </c>
       <c r="E28" t="n">
-        <v>600000</v>
+        <v>591601</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kabupaten Malang</t>
+          <t>Kota Malang</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3247,7 +3247,7 @@
         <v>195000</v>
       </c>
       <c r="I28" t="n">
-        <v>285000</v>
+        <v>275000</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -3256,30 +3256,30 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
+          <t>Depot 59</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>55500</v>
+        <v>95000</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Depot 88 - Araya</t>
+          <t>Depot Gang Djangkrik</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>58750</v>
+        <v>65714</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>DAPUR LAWAS MALANG</t>
+          <t>Depot Kanton</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>58500</v>
+        <v>65000</v>
       </c>
       <c r="Q28" t="n">
-        <v>286750</v>
+        <v>356428</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="S28" t="n">
-        <v>99.92</v>
+        <v>80.45</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3295,16 +3295,16 @@
         </is>
       </c>
       <c r="U28" t="n">
-        <v>224814</v>
+        <v>181022</v>
       </c>
       <c r="V28" t="n">
-        <v>1396564</v>
+        <v>1404051</v>
       </c>
       <c r="W28" t="n">
         <v>1500000</v>
       </c>
       <c r="X28" t="n">
-        <v>103436</v>
+        <v>95949</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Kos Putra Bulanan</t>
+          <t>THE 1O1 Malang OJ</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -4191,7 +4191,7 @@
         <v>717973</v>
       </c>
       <c r="AB4" t="n">
-        <v>600000</v>
+        <v>591601</v>
       </c>
       <c r="AC4" t="n">
         <v>813000</v>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
+          <t>Depot 59</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -4699,7 +4699,7 @@
         <v>41600</v>
       </c>
       <c r="AB8" t="n">
-        <v>55500</v>
+        <v>95000</v>
       </c>
       <c r="AC8" t="n">
         <v>51182</v>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Depot 88 - Araya</t>
+          <t>Depot Gang Djangkrik</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4953,7 +4953,7 @@
         <v>53500</v>
       </c>
       <c r="AB10" t="n">
-        <v>58750</v>
+        <v>65714</v>
       </c>
       <c r="AC10" t="n">
         <v>49665</v>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>DAPUR LAWAS MALANG</t>
+          <t>Depot Kanton</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5207,7 +5207,7 @@
         <v>41337</v>
       </c>
       <c r="AB12" t="n">
-        <v>58500</v>
+        <v>65000</v>
       </c>
       <c r="AC12" t="n">
         <v>41337</v>
@@ -5304,7 +5304,7 @@
         <v>717973</v>
       </c>
       <c r="AB13" t="n">
-        <v>600000</v>
+        <v>591601</v>
       </c>
       <c r="AC13" t="n">
         <v>813000</v>
@@ -5498,7 +5498,7 @@
         <v>136437</v>
       </c>
       <c r="AB15" t="n">
-        <v>172750</v>
+        <v>225714</v>
       </c>
       <c r="AC15" t="n">
         <v>142184</v>
@@ -5595,7 +5595,7 @@
         <v>148120</v>
       </c>
       <c r="AB16" t="n">
-        <v>112407</v>
+        <v>90511</v>
       </c>
       <c r="AC16" t="n">
         <v>31296</v>
@@ -5692,7 +5692,7 @@
         <v>62.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>35.51</v>
+        <v>34.9</v>
       </c>
       <c r="AC17" t="n">
         <v>5.37</v>
@@ -5789,7 +5789,7 @@
         <v>57.22</v>
       </c>
       <c r="AB18" t="n">
-        <v>32.95</v>
+        <v>35.53</v>
       </c>
       <c r="AC18" t="n">
         <v>5.51</v>
@@ -5886,7 +5886,7 @@
         <v>6.52</v>
       </c>
       <c r="AB19" t="n">
-        <v>10.19</v>
+        <v>1.87</v>
       </c>
       <c r="AC19" t="n">
         <v>3.87</v>
@@ -5983,7 +5983,7 @@
         <v>0.44</v>
       </c>
       <c r="AB20" t="n">
-        <v>4.94</v>
+        <v>1.4</v>
       </c>
       <c r="AC20" t="n">
         <v>1.4</v>
@@ -6080,7 +6080,7 @@
         <v>0.44</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.94</v>
+        <v>1.4</v>
       </c>
       <c r="AC21" t="n">
         <v>1.4</v>
@@ -6177,7 +6177,7 @@
         <v>127.13</v>
       </c>
       <c r="AB22" t="n">
-        <v>88.53</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AC22" t="n">
         <v>17.56</v>
@@ -6274,7 +6274,7 @@
         <v>1077530</v>
       </c>
       <c r="AB23" t="n">
-        <v>1080157</v>
+        <v>1102826</v>
       </c>
       <c r="AC23" t="n">
         <v>1186480</v>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Lampion &amp; Dinosaurus Park</t>
+          <t>Taman Indragiri Malang</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -6782,7 +6782,7 @@
         <v>185000</v>
       </c>
       <c r="AB27" t="n">
-        <v>90000</v>
+        <v>80000</v>
       </c>
       <c r="AC27" t="n">
         <v>155000</v>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Kantri Masakan Indonesia &amp; Sea Food</t>
+          <t>Depot Gang Djangkrik</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -7036,7 +7036,7 @@
         <v>41600</v>
       </c>
       <c r="AB29" t="n">
-        <v>55500</v>
+        <v>65714</v>
       </c>
       <c r="AC29" t="n">
         <v>41337</v>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>DAPUR LAWAS MALANG</t>
+          <t>Depot Kanton</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -7290,7 +7290,7 @@
         <v>41337</v>
       </c>
       <c r="AB31" t="n">
-        <v>58500</v>
+        <v>65000</v>
       </c>
       <c r="AC31" t="n">
         <v>42000</v>
@@ -7738,7 +7738,7 @@
         <v>185000</v>
       </c>
       <c r="AB35" t="n">
-        <v>90000</v>
+        <v>80000</v>
       </c>
       <c r="AC35" t="n">
         <v>155000</v>
@@ -7835,7 +7835,7 @@
         <v>82937</v>
       </c>
       <c r="AB36" t="n">
-        <v>114000</v>
+        <v>130714</v>
       </c>
       <c r="AC36" t="n">
         <v>83337</v>
@@ -7932,7 +7932,7 @@
         <v>148119</v>
       </c>
       <c r="AB37" t="n">
-        <v>112407</v>
+        <v>90511</v>
       </c>
       <c r="AC37" t="n">
         <v>31297</v>
@@ -8029,7 +8029,7 @@
         <v>1.73</v>
       </c>
       <c r="AB38" t="n">
-        <v>5.08</v>
+        <v>1.87</v>
       </c>
       <c r="AC38" t="n">
         <v>1.4</v>
@@ -8126,7 +8126,7 @@
         <v>1.9</v>
       </c>
       <c r="AB39" t="n">
-        <v>3.48</v>
+        <v>0.58</v>
       </c>
       <c r="AC39" t="n">
         <v>6.37</v>
@@ -8223,7 +8223,7 @@
         <v>0.91</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="AC40" t="n">
         <v>2.48</v>
@@ -8320,7 +8320,7 @@
         <v>4.53</v>
       </c>
       <c r="AB41" t="n">
-        <v>11.38</v>
+        <v>5.36</v>
       </c>
       <c r="AC41" t="n">
         <v>10.26</v>
@@ -8417,7 +8417,7 @@
         <v>416056</v>
       </c>
       <c r="AB42" t="n">
-        <v>316407</v>
+        <v>301225</v>
       </c>
       <c r="AC42" t="n">
         <v>269634</v>
@@ -8514,7 +8514,7 @@
         <v>717973</v>
       </c>
       <c r="AB43" t="n">
-        <v>600000</v>
+        <v>591601</v>
       </c>
       <c r="AC43" t="n">
         <v>813000</v>
@@ -8611,7 +8611,7 @@
         <v>260000</v>
       </c>
       <c r="AB44" t="n">
-        <v>285000</v>
+        <v>275000</v>
       </c>
       <c r="AC44" t="n">
         <v>355000</v>
@@ -8708,7 +8708,7 @@
         <v>219374</v>
       </c>
       <c r="AB45" t="n">
-        <v>286750</v>
+        <v>356428</v>
       </c>
       <c r="AC45" t="n">
         <v>225521</v>
@@ -8805,7 +8805,7 @@
         <v>296239</v>
       </c>
       <c r="AB46" t="n">
-        <v>224814</v>
+        <v>181022</v>
       </c>
       <c r="AC46" t="n">
         <v>62593</v>
@@ -8902,7 +8902,7 @@
         <v>1493586</v>
       </c>
       <c r="AB47" t="n">
-        <v>1396564</v>
+        <v>1404051</v>
       </c>
       <c r="AC47" t="n">
         <v>1456114</v>
@@ -8999,7 +8999,7 @@
         <v>131.66</v>
       </c>
       <c r="AB48" t="n">
-        <v>99.92</v>
+        <v>80.45</v>
       </c>
       <c r="AC48" t="n">
         <v>27.82</v>
@@ -9096,7 +9096,7 @@
         <v>6414</v>
       </c>
       <c r="AB49" t="n">
-        <v>103436</v>
+        <v>95949</v>
       </c>
       <c r="AC49" t="n">
         <v>43886</v>
